--- a/data/trans_orig/P05A01-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P05A01-Edad-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si en el barrio donde vive el ruido procedente del exterior de su vivienda le resulta molesto en 2007</t>
+          <t>Población según si en el barrio donde vive el ruido procedente del exterior de su vivienda le resulta molesto en 2007 (tasa de respuesta: 99,91%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>250706</t>
+          <t>251764</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>293401</t>
+          <t>296051</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>50,74%</t>
+          <t>50,96%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>59,39%</t>
+          <t>59,92%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>227115</t>
+          <t>227492</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>268559</t>
+          <t>268973</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>48,68%</t>
+          <t>48,77%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>57,57%</t>
+          <t>57,66%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>492965</t>
+          <t>489892</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>552359</t>
+          <t>551171</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>51,32%</t>
+          <t>51,0%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>57,5%</t>
+          <t>57,38%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>162779</t>
+          <t>162622</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>206144</t>
+          <t>204020</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>32,95%</t>
+          <t>32,92%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>41,72%</t>
+          <t>41,29%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>146013</t>
+          <t>147425</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>186542</t>
+          <t>186821</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>31,3%</t>
+          <t>31,6%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>39,99%</t>
+          <t>40,05%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>322477</t>
+          <t>323199</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>380503</t>
+          <t>380645</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>33,57%</t>
+          <t>33,65%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>39,61%</t>
+          <t>39,63%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>26259</t>
+          <t>27118</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>49295</t>
+          <t>49759</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>5,49%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>9,98%</t>
+          <t>10,07%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>39667</t>
+          <t>39644</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>68028</t>
+          <t>67120</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1014,7 +1014,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>14,58%</t>
+          <t>14,39%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>71771</t>
+          <t>71762</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>105178</t>
+          <t>105504</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1049,7 +1049,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>10,95%</t>
+          <t>10,98%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>368692</t>
+          <t>371077</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>424781</t>
+          <t>425404</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>50,13%</t>
+          <t>50,45%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>57,75%</t>
+          <t>57,84%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>270227</t>
+          <t>267316</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>325422</t>
+          <t>320005</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>43,2%</t>
+          <t>42,74%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>52,03%</t>
+          <t>51,16%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>655447</t>
+          <t>654811</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>731556</t>
+          <t>728398</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>48,16%</t>
+          <t>48,11%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>53,75%</t>
+          <t>53,52%</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>237669</t>
+          <t>236467</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>292141</t>
+          <t>286742</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>32,31%</t>
+          <t>32,15%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>39,72%</t>
+          <t>38,99%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>231478</t>
+          <t>230780</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>282732</t>
+          <t>281346</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1352,12 +1352,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>37,01%</t>
+          <t>36,9%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>45,2%</t>
+          <t>44,98%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>483940</t>
+          <t>480314</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>560784</t>
+          <t>556571</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>35,56%</t>
+          <t>35,29%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>41,2%</t>
+          <t>40,89%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>58461</t>
+          <t>57689</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>91696</t>
+          <t>93022</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>7,95%</t>
+          <t>7,84%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>12,47%</t>
+          <t>12,65%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>57467</t>
+          <t>57902</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>92800</t>
+          <t>92550</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>9,19%</t>
+          <t>9,26%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>14,84%</t>
+          <t>14,8%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>125933</t>
+          <t>125384</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>174602</t>
+          <t>172580</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>9,25%</t>
+          <t>9,21%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>12,83%</t>
+          <t>12,68%</t>
         </is>
       </c>
     </row>
@@ -1645,12 +1645,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>314771</t>
+          <t>315138</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>366107</t>
+          <t>366006</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1660,12 +1660,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>49,29%</t>
+          <t>49,34%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>57,32%</t>
+          <t>57,31%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1680,12 +1680,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>316815</t>
+          <t>313240</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>367257</t>
+          <t>369023</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1695,12 +1695,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>45,93%</t>
+          <t>45,41%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>53,25%</t>
+          <t>53,5%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1715,12 +1715,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>644221</t>
+          <t>643125</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>717569</t>
+          <t>718098</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1730,12 +1730,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>48,5%</t>
+          <t>48,41%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>54,02%</t>
+          <t>54,06%</t>
         </is>
       </c>
     </row>
@@ -1758,12 +1758,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>214463</t>
+          <t>215685</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>262591</t>
+          <t>266172</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1773,12 +1773,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>33,58%</t>
+          <t>33,77%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>41,12%</t>
+          <t>41,68%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1793,12 +1793,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>216244</t>
+          <t>216305</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>266458</t>
+          <t>267118</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1808,12 +1808,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>31,35%</t>
+          <t>31,36%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>38,63%</t>
+          <t>38,73%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1828,12 +1828,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>442094</t>
+          <t>446514</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>512990</t>
+          <t>515699</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1843,12 +1843,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>33,28%</t>
+          <t>33,61%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>38,62%</t>
+          <t>38,82%</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>45144</t>
+          <t>44761</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>75697</t>
+          <t>75639</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>7,07%</t>
+          <t>7,01%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>11,85%</t>
+          <t>11,84%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>90713</t>
+          <t>89000</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>128580</t>
+          <t>129242</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>13,15%</t>
+          <t>12,9%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>18,64%</t>
+          <t>18,74%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>144066</t>
+          <t>143452</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>192999</t>
+          <t>194335</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>10,84%</t>
+          <t>10,8%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>14,53%</t>
+          <t>14,63%</t>
         </is>
       </c>
     </row>
@@ -2101,12 +2101,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>246907</t>
+          <t>247685</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>293969</t>
+          <t>295820</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2116,12 +2116,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>47,56%</t>
+          <t>47,71%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>56,63%</t>
+          <t>56,98%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2136,12 +2136,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>246853</t>
+          <t>246353</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>293805</t>
+          <t>292279</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2151,12 +2151,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>48,05%</t>
+          <t>47,95%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>57,19%</t>
+          <t>56,89%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>507953</t>
+          <t>510492</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>571945</t>
+          <t>574539</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2186,12 +2186,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>49,18%</t>
+          <t>49,42%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>55,37%</t>
+          <t>55,62%</t>
         </is>
       </c>
     </row>
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>169511</t>
+          <t>168924</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>215947</t>
+          <t>214556</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2229,12 +2229,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>32,65%</t>
+          <t>32,54%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>41,6%</t>
+          <t>41,33%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2249,12 +2249,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>149338</t>
+          <t>153570</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>192096</t>
+          <t>195571</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2264,12 +2264,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>29,07%</t>
+          <t>29,89%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>37,39%</t>
+          <t>38,07%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2284,12 +2284,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>334443</t>
+          <t>333256</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>398392</t>
+          <t>396457</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>32,38%</t>
+          <t>32,26%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>38,57%</t>
+          <t>38,38%</t>
         </is>
       </c>
     </row>
@@ -2327,12 +2327,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>43600</t>
+          <t>42818</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>72729</t>
+          <t>70399</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2342,12 +2342,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>8,4%</t>
+          <t>8,25%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>14,01%</t>
+          <t>13,56%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2362,12 +2362,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>57370</t>
+          <t>57147</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>88004</t>
+          <t>87824</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2377,12 +2377,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>11,17%</t>
+          <t>11,12%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>17,13%</t>
+          <t>17,1%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2397,12 +2397,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>108145</t>
+          <t>108146</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>147609</t>
+          <t>150788</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2417,7 +2417,7 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>14,29%</t>
+          <t>14,6%</t>
         </is>
       </c>
     </row>
@@ -2557,12 +2557,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>181262</t>
+          <t>179828</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>219731</t>
+          <t>219523</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2572,12 +2572,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>46,98%</t>
+          <t>46,6%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>56,94%</t>
+          <t>56,89%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2592,12 +2592,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>186026</t>
+          <t>186700</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>226110</t>
+          <t>226440</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2607,12 +2607,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>46,15%</t>
+          <t>46,32%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>56,1%</t>
+          <t>56,18%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>380537</t>
+          <t>380167</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>433577</t>
+          <t>432258</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2642,12 +2642,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>48,24%</t>
+          <t>48,19%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>54,96%</t>
+          <t>54,79%</t>
         </is>
       </c>
     </row>
@@ -2670,12 +2670,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>119273</t>
+          <t>120758</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>156516</t>
+          <t>157750</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2685,12 +2685,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>30,91%</t>
+          <t>31,3%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>40,56%</t>
+          <t>40,88%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2705,12 +2705,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>115270</t>
+          <t>114281</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>152850</t>
+          <t>151141</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2720,12 +2720,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>28,6%</t>
+          <t>28,35%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>37,92%</t>
+          <t>37,5%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2740,12 +2740,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>243233</t>
+          <t>244957</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>298679</t>
+          <t>297801</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2755,12 +2755,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>30,83%</t>
+          <t>31,05%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>37,86%</t>
+          <t>37,75%</t>
         </is>
       </c>
     </row>
@@ -2783,12 +2783,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>35078</t>
+          <t>35715</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>61790</t>
+          <t>62384</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2798,12 +2798,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>9,09%</t>
+          <t>9,26%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>16,01%</t>
+          <t>16,17%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2818,12 +2818,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>49108</t>
+          <t>50465</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>77887</t>
+          <t>78940</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2833,12 +2833,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>12,18%</t>
+          <t>12,52%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>19,32%</t>
+          <t>19,59%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,12 +2853,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>93596</t>
+          <t>93969</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>131477</t>
+          <t>132060</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2868,12 +2868,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>11,86%</t>
+          <t>11,91%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>16,67%</t>
+          <t>16,74%</t>
         </is>
       </c>
     </row>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>127090</t>
+          <t>127028</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>159009</t>
+          <t>160796</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3028,12 +3028,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>43,44%</t>
+          <t>43,42%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>54,35%</t>
+          <t>54,96%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3048,12 +3048,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>150238</t>
+          <t>150348</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>184941</t>
+          <t>186711</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3063,12 +3063,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>43,81%</t>
+          <t>43,84%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>53,93%</t>
+          <t>54,45%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3083,12 +3083,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>288736</t>
+          <t>288965</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>335099</t>
+          <t>334554</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3098,12 +3098,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>45,43%</t>
+          <t>45,47%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>52,73%</t>
+          <t>52,64%</t>
         </is>
       </c>
     </row>
@@ -3126,12 +3126,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>103187</t>
+          <t>102450</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>135664</t>
+          <t>135615</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3141,12 +3141,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>35,27%</t>
+          <t>35,02%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>46,37%</t>
+          <t>46,35%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3161,12 +3161,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>111189</t>
+          <t>111385</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>144776</t>
+          <t>146298</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3176,12 +3176,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>32,42%</t>
+          <t>32,48%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>42,22%</t>
+          <t>42,66%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3196,12 +3196,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>223826</t>
+          <t>224323</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>269959</t>
+          <t>269321</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3211,12 +3211,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>35,22%</t>
+          <t>35,3%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>42,48%</t>
+          <t>42,38%</t>
         </is>
       </c>
     </row>
@@ -3239,12 +3239,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>22030</t>
+          <t>22001</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>42612</t>
+          <t>42081</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3254,12 +3254,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>7,53%</t>
+          <t>7,52%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>14,56%</t>
+          <t>14,38%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3274,12 +3274,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>35716</t>
+          <t>36127</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>59782</t>
+          <t>59384</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3289,12 +3289,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>10,41%</t>
+          <t>10,53%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>17,43%</t>
+          <t>17,32%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3309,12 +3309,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>61800</t>
+          <t>63616</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>93983</t>
+          <t>93399</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>9,72%</t>
+          <t>10,01%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>14,79%</t>
+          <t>14,7%</t>
         </is>
       </c>
     </row>
@@ -3469,12 +3469,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>91170</t>
+          <t>91021</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>118922</t>
+          <t>117825</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3484,12 +3484,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>43,62%</t>
+          <t>43,55%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>56,9%</t>
+          <t>56,37%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3504,12 +3504,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>149503</t>
+          <t>149752</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>188819</t>
+          <t>188050</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3519,12 +3519,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>44,77%</t>
+          <t>44,85%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>56,55%</t>
+          <t>56,32%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3539,12 +3539,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>250448</t>
+          <t>251173</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>297171</t>
+          <t>298803</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3554,12 +3554,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>46,13%</t>
+          <t>46,26%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>54,74%</t>
+          <t>55,04%</t>
         </is>
       </c>
     </row>
@@ -3582,12 +3582,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>66762</t>
+          <t>67919</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>94659</t>
+          <t>94184</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3597,12 +3597,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>31,94%</t>
+          <t>32,49%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>45,29%</t>
+          <t>45,06%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3617,12 +3617,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>103729</t>
+          <t>105716</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>142044</t>
+          <t>143273</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3632,12 +3632,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>31,07%</t>
+          <t>31,66%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>42,54%</t>
+          <t>42,91%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3652,12 +3652,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>183507</t>
+          <t>182948</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>226784</t>
+          <t>227723</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3667,12 +3667,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>33,8%</t>
+          <t>33,7%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>41,77%</t>
+          <t>41,94%</t>
         </is>
       </c>
     </row>
@@ -3695,12 +3695,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>14732</t>
+          <t>14977</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>32456</t>
+          <t>33531</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3710,12 +3710,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>7,05%</t>
+          <t>7,17%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>15,53%</t>
+          <t>16,04%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3730,12 +3730,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>29174</t>
+          <t>28919</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>55283</t>
+          <t>54868</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3745,12 +3745,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>8,74%</t>
+          <t>8,66%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>16,56%</t>
+          <t>16,43%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3765,12 +3765,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>50764</t>
+          <t>50706</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>82190</t>
+          <t>79950</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3780,12 +3780,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>9,35%</t>
+          <t>9,34%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>15,14%</t>
+          <t>14,73%</t>
         </is>
       </c>
     </row>
@@ -3925,12 +3925,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>1671918</t>
+          <t>1671606</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>1787667</t>
+          <t>1788804</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3940,12 +3940,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>51,05%</t>
+          <t>51,04%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>54,59%</t>
+          <t>54,62%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3960,12 +3960,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>1640577</t>
+          <t>1638876</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>1756357</t>
+          <t>1753476</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3975,12 +3975,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>48,6%</t>
+          <t>48,55%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>52,03%</t>
+          <t>51,95%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3995,12 +3995,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>3356520</t>
+          <t>3340558</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>3518119</t>
+          <t>3503987</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -4010,12 +4010,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>50,47%</t>
+          <t>50,23%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>52,9%</t>
+          <t>52,69%</t>
         </is>
       </c>
     </row>
@@ -4038,12 +4038,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>1164232</t>
+          <t>1162947</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>1277100</t>
+          <t>1272086</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4053,12 +4053,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>35,55%</t>
+          <t>35,51%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>39,0%</t>
+          <t>38,84%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -4073,12 +4073,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>1168636</t>
+          <t>1168849</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>1280920</t>
+          <t>1275453</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4088,12 +4088,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>34,62%</t>
+          <t>34,63%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>37,95%</t>
+          <t>37,79%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4108,12 +4108,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>2359015</t>
+          <t>2360398</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>2512847</t>
+          <t>2519056</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4123,12 +4123,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>35,47%</t>
+          <t>35,49%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>37,79%</t>
+          <t>37,88%</t>
         </is>
       </c>
     </row>
@@ -4151,12 +4151,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>296613</t>
+          <t>293495</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>362488</t>
+          <t>362341</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4166,12 +4166,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>9,06%</t>
+          <t>8,96%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>11,07%</t>
+          <t>11,06%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4186,12 +4186,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>414955</t>
+          <t>420122</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>495318</t>
+          <t>495299</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4201,7 +4201,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>12,29%</t>
+          <t>12,45%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4221,12 +4221,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>723227</t>
+          <t>734002</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>836954</t>
+          <t>836581</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4236,12 +4236,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>10,88%</t>
+          <t>11,04%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>12,59%</t>
+          <t>12,58%</t>
         </is>
       </c>
     </row>
@@ -4421,7 +4421,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si en el barrio donde vive el ruido procedente del exterior de su vivienda le resulta molesto en 2012</t>
+          <t>Población según si en el barrio donde vive el ruido procedente del exterior de su vivienda le resulta molesto en 2012 (tasa de respuesta: 99,83%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4616,12 +4616,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>293964</t>
+          <t>295772</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>333822</t>
+          <t>333603</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4631,12 +4631,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>64,86%</t>
+          <t>65,26%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>73,66%</t>
+          <t>73,61%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4651,12 +4651,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>289895</t>
+          <t>292417</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>328111</t>
+          <t>329580</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4666,12 +4666,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>67,54%</t>
+          <t>68,13%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>76,44%</t>
+          <t>76,79%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4686,12 +4686,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>596899</t>
+          <t>597995</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>652918</t>
+          <t>650248</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4701,12 +4701,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>67,64%</t>
+          <t>67,77%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>73,99%</t>
+          <t>73,69%</t>
         </is>
       </c>
     </row>
@@ -4729,12 +4729,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>99265</t>
+          <t>99330</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>137164</t>
+          <t>135693</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4744,12 +4744,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>21,9%</t>
+          <t>21,92%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>30,27%</t>
+          <t>29,94%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4764,12 +4764,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>85474</t>
+          <t>83689</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>122147</t>
+          <t>120217</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4779,12 +4779,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>19,91%</t>
+          <t>19,5%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>28,46%</t>
+          <t>28,01%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4799,12 +4799,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>193815</t>
+          <t>196890</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>246577</t>
+          <t>247648</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4814,12 +4814,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>21,96%</t>
+          <t>22,31%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>27,94%</t>
+          <t>28,06%</t>
         </is>
       </c>
     </row>
@@ -4842,12 +4842,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>12798</t>
+          <t>13690</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>30396</t>
+          <t>31785</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4857,12 +4857,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>6,71%</t>
+          <t>7,01%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4877,12 +4877,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>10029</t>
+          <t>9711</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>26783</t>
+          <t>26742</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4892,12 +4892,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>6,23%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4912,12 +4912,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>27110</t>
+          <t>26493</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>51019</t>
+          <t>51346</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4927,12 +4927,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>5,82%</t>
         </is>
       </c>
     </row>
@@ -5072,12 +5072,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>446020</t>
+          <t>443922</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>491935</t>
+          <t>492609</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5087,12 +5087,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>65,06%</t>
+          <t>64,75%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>71,76%</t>
+          <t>71,86%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5107,12 +5107,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>400458</t>
+          <t>404928</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>450009</t>
+          <t>451021</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5122,12 +5122,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>65,62%</t>
+          <t>66,35%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>73,74%</t>
+          <t>73,91%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5142,12 +5142,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>862188</t>
+          <t>859078</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>934096</t>
+          <t>926848</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5157,12 +5157,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>66,54%</t>
+          <t>66,3%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>72,09%</t>
+          <t>71,53%</t>
         </is>
       </c>
     </row>
@@ -5185,12 +5185,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>146330</t>
+          <t>147861</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>192245</t>
+          <t>193064</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -5200,12 +5200,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>21,35%</t>
+          <t>21,57%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>28,04%</t>
+          <t>28,16%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -5220,12 +5220,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>118387</t>
+          <t>119327</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>164153</t>
+          <t>161673</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5235,12 +5235,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>19,4%</t>
+          <t>19,55%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>26,9%</t>
+          <t>26,49%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -5255,12 +5255,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>276883</t>
+          <t>280236</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>339832</t>
+          <t>344694</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -5270,12 +5270,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>21,37%</t>
+          <t>21,63%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>26,23%</t>
+          <t>26,6%</t>
         </is>
       </c>
     </row>
@@ -5298,12 +5298,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>35374</t>
+          <t>34398</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>62190</t>
+          <t>62312</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5313,12 +5313,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>5,02%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>9,07%</t>
+          <t>9,09%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5333,12 +5333,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>32878</t>
+          <t>31822</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>58608</t>
+          <t>57753</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>5,21%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>9,6%</t>
+          <t>9,46%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5368,12 +5368,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>73284</t>
+          <t>72108</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>113190</t>
+          <t>111124</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>5,56%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>8,74%</t>
+          <t>8,58%</t>
         </is>
       </c>
     </row>
@@ -5528,12 +5528,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>444084</t>
+          <t>445809</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>496201</t>
+          <t>497533</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5543,12 +5543,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>65,28%</t>
+          <t>65,54%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>72,94%</t>
+          <t>73,14%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5563,12 +5563,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>497096</t>
+          <t>494105</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>543750</t>
+          <t>546901</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5578,12 +5578,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>70,1%</t>
+          <t>69,68%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>76,68%</t>
+          <t>77,12%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5598,12 +5598,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>959329</t>
+          <t>963290</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1027327</t>
+          <t>1031869</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5613,12 +5613,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>69,05%</t>
+          <t>69,33%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>73,94%</t>
+          <t>74,27%</t>
         </is>
       </c>
     </row>
@@ -5641,12 +5641,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>145946</t>
+          <t>144136</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>192938</t>
+          <t>190939</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5656,12 +5656,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>21,46%</t>
+          <t>21,19%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>28,36%</t>
+          <t>28,07%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5676,12 +5676,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>124006</t>
+          <t>121624</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>165853</t>
+          <t>167718</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>17,49%</t>
+          <t>17,15%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>23,39%</t>
+          <t>23,65%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5711,12 +5711,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>281244</t>
+          <t>280317</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>345249</t>
+          <t>340276</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>20,24%</t>
+          <t>20,18%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>24,85%</t>
+          <t>24,49%</t>
         </is>
       </c>
     </row>
@@ -5754,12 +5754,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>29421</t>
+          <t>29216</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>56910</t>
+          <t>55638</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5769,12 +5769,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,29%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>8,37%</t>
+          <t>8,18%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5789,12 +5789,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>31651</t>
+          <t>31748</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>57471</t>
+          <t>59042</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,48%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>8,1%</t>
+          <t>8,33%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5824,12 +5824,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>67566</t>
+          <t>66570</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>103728</t>
+          <t>103084</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>4,79%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>7,47%</t>
+          <t>7,42%</t>
         </is>
       </c>
     </row>
@@ -5984,12 +5984,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>384173</t>
+          <t>387189</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>431992</t>
+          <t>437604</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5999,12 +5999,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>62,61%</t>
+          <t>63,1%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>70,4%</t>
+          <t>71,32%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6019,12 +6019,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>405083</t>
+          <t>407559</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>454646</t>
+          <t>454831</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>65,85%</t>
+          <t>66,25%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>73,91%</t>
+          <t>73,94%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6054,12 +6054,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>806016</t>
+          <t>807790</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>877069</t>
+          <t>876533</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>65,6%</t>
+          <t>65,74%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>71,38%</t>
+          <t>71,34%</t>
         </is>
       </c>
     </row>
@@ -6097,12 +6097,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>139355</t>
+          <t>138321</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>185948</t>
+          <t>186280</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6112,12 +6112,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>22,71%</t>
+          <t>22,54%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>30,3%</t>
+          <t>30,36%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6132,12 +6132,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>110694</t>
+          <t>110898</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>152642</t>
+          <t>153857</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>18,0%</t>
+          <t>18,03%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>24,81%</t>
+          <t>25,01%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6167,12 +6167,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>258337</t>
+          <t>261175</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>325199</t>
+          <t>327232</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>21,02%</t>
+          <t>21,26%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>26,47%</t>
+          <t>26,63%</t>
         </is>
       </c>
     </row>
@@ -6210,12 +6210,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>29828</t>
+          <t>30022</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>56602</t>
+          <t>55718</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -6225,12 +6225,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>4,89%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>9,22%</t>
+          <t>9,08%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6245,12 +6245,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>37318</t>
+          <t>39112</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>67681</t>
+          <t>69337</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6260,12 +6260,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>6,36%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>11,0%</t>
+          <t>11,27%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6280,12 +6280,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>74763</t>
+          <t>75732</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>114799</t>
+          <t>114788</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6295,7 +6295,7 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>6,16%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
@@ -6440,12 +6440,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>285416</t>
+          <t>284066</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>324225</t>
+          <t>323463</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6455,12 +6455,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>66,46%</t>
+          <t>66,15%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>75,5%</t>
+          <t>75,32%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6475,12 +6475,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>282737</t>
+          <t>283266</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>323391</t>
+          <t>323513</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6490,12 +6490,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>63,43%</t>
+          <t>63,55%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>72,55%</t>
+          <t>72,58%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6510,12 +6510,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>581429</t>
+          <t>578169</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>635932</t>
+          <t>635158</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6525,12 +6525,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>66,44%</t>
+          <t>66,06%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>72,66%</t>
+          <t>72,58%</t>
         </is>
       </c>
     </row>
@@ -6553,12 +6553,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>83958</t>
+          <t>83847</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>121401</t>
+          <t>120075</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -6568,12 +6568,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>19,55%</t>
+          <t>19,53%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>28,27%</t>
+          <t>27,96%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -6588,12 +6588,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>91525</t>
+          <t>91494</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>129537</t>
+          <t>130839</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -6608,7 +6608,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>29,06%</t>
+          <t>29,35%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -6623,12 +6623,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>185940</t>
+          <t>186943</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>236089</t>
+          <t>241312</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -6638,12 +6638,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>21,25%</t>
+          <t>21,36%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>26,98%</t>
+          <t>27,57%</t>
         </is>
       </c>
     </row>
@@ -6666,12 +6666,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>14773</t>
+          <t>14945</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>34134</t>
+          <t>33923</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6681,12 +6681,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>7,95%</t>
+          <t>7,9%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6701,12 +6701,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>22642</t>
+          <t>22972</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>44405</t>
+          <t>45497</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6716,12 +6716,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>5,15%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>9,96%</t>
+          <t>10,21%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6736,12 +6736,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>41176</t>
+          <t>43037</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>73263</t>
+          <t>71879</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6751,12 +6751,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>8,37%</t>
+          <t>8,21%</t>
         </is>
       </c>
     </row>
@@ -6896,12 +6896,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>178882</t>
+          <t>177572</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>213940</t>
+          <t>214973</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6911,12 +6911,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>57,74%</t>
+          <t>57,32%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>69,06%</t>
+          <t>69,39%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6931,12 +6931,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>217162</t>
+          <t>217266</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>252906</t>
+          <t>252985</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6946,12 +6946,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>61,35%</t>
+          <t>61,38%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>71,44%</t>
+          <t>71,47%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6966,12 +6966,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>406495</t>
+          <t>407119</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>455517</t>
+          <t>457939</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6981,12 +6981,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>61,24%</t>
+          <t>61,33%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>68,62%</t>
+          <t>68,99%</t>
         </is>
       </c>
     </row>
@@ -7009,12 +7009,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>66558</t>
+          <t>67331</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>99740</t>
+          <t>100418</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -7024,12 +7024,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>21,48%</t>
+          <t>21,73%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>32,2%</t>
+          <t>32,42%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -7044,12 +7044,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>73468</t>
+          <t>73477</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>105136</t>
+          <t>106360</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>20,75%</t>
+          <t>20,76%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>29,7%</t>
+          <t>30,05%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -7079,12 +7079,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>150005</t>
+          <t>149428</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>196766</t>
+          <t>196578</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -7094,12 +7094,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>22,6%</t>
+          <t>22,51%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>29,64%</t>
+          <t>29,61%</t>
         </is>
       </c>
     </row>
@@ -7122,12 +7122,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>20533</t>
+          <t>20462</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>44345</t>
+          <t>42770</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -7137,12 +7137,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>6,61%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>14,31%</t>
+          <t>13,81%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -7157,12 +7157,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>19406</t>
+          <t>19214</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>41401</t>
+          <t>40616</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -7172,12 +7172,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>5,43%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>11,7%</t>
+          <t>11,47%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -7192,12 +7192,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>45366</t>
+          <t>45186</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>77137</t>
+          <t>76645</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -7207,12 +7207,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>6,83%</t>
+          <t>6,81%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>11,62%</t>
+          <t>11,55%</t>
         </is>
       </c>
     </row>
@@ -7352,12 +7352,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>153026</t>
+          <t>153335</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>186155</t>
+          <t>185423</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -7367,12 +7367,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>61,53%</t>
+          <t>61,66%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>74,86%</t>
+          <t>74,56%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -7387,12 +7387,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>247866</t>
+          <t>248171</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>284270</t>
+          <t>286998</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -7402,12 +7402,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>63,72%</t>
+          <t>63,8%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>73,08%</t>
+          <t>73,78%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -7422,12 +7422,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>411900</t>
+          <t>413941</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>461461</t>
+          <t>460226</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -7437,12 +7437,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>64,6%</t>
+          <t>64,92%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>72,37%</t>
+          <t>72,17%</t>
         </is>
       </c>
     </row>
@@ -7465,12 +7465,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>51002</t>
+          <t>50740</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>80933</t>
+          <t>80795</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7480,12 +7480,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>20,51%</t>
+          <t>20,4%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>32,54%</t>
+          <t>32,49%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7500,12 +7500,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>85727</t>
+          <t>84556</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>121101</t>
+          <t>121769</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7515,12 +7515,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>22,04%</t>
+          <t>21,74%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>31,13%</t>
+          <t>31,3%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7535,12 +7535,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>145976</t>
+          <t>145407</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>192012</t>
+          <t>191199</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7550,12 +7550,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>22,89%</t>
+          <t>22,8%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>30,11%</t>
+          <t>29,98%</t>
         </is>
       </c>
     </row>
@@ -7578,12 +7578,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>7177</t>
+          <t>7321</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>22356</t>
+          <t>22424</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7593,12 +7593,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>8,99%</t>
+          <t>9,02%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7613,12 +7613,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>11642</t>
+          <t>11801</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>30651</t>
+          <t>29114</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7628,12 +7628,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>7,88%</t>
+          <t>7,48%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7648,12 +7648,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>22243</t>
+          <t>22871</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>45765</t>
+          <t>46400</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7663,12 +7663,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>7,18%</t>
+          <t>7,28%</t>
         </is>
       </c>
     </row>
@@ -7808,12 +7808,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>2282682</t>
+          <t>2286459</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>2396489</t>
+          <t>2394117</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -7823,12 +7823,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>66,74%</t>
+          <t>66,85%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>70,06%</t>
+          <t>69,99%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -7843,12 +7843,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>2439274</t>
+          <t>2435719</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>2549770</t>
+          <t>2551859</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -7858,12 +7858,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>68,66%</t>
+          <t>68,56%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>71,77%</t>
+          <t>71,83%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -7878,12 +7878,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>4760047</t>
+          <t>4765199</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>4918867</t>
+          <t>4919501</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -7893,12 +7893,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>68,26%</t>
+          <t>68,34%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>70,54%</t>
+          <t>70,55%</t>
         </is>
       </c>
     </row>
@@ -7921,12 +7921,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>815909</t>
+          <t>813418</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>918403</t>
+          <t>917529</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -7936,12 +7936,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>23,85%</t>
+          <t>23,78%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>26,85%</t>
+          <t>26,82%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -7956,12 +7956,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>773161</t>
+          <t>767178</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>874913</t>
+          <t>872355</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -7971,12 +7971,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>21,76%</t>
+          <t>21,6%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>24,63%</t>
+          <t>24,56%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -7991,12 +7991,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>1611615</t>
+          <t>1614482</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>1756750</t>
+          <t>1749883</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -8006,12 +8006,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>23,11%</t>
+          <t>23,15%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>25,19%</t>
+          <t>25,1%</t>
         </is>
       </c>
     </row>
@@ -8034,12 +8034,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>186662</t>
+          <t>188398</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>245324</t>
+          <t>248313</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -8049,12 +8049,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>5,51%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>7,17%</t>
+          <t>7,26%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -8069,12 +8069,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>206727</t>
+          <t>209362</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>268851</t>
+          <t>271966</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -8084,12 +8084,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>5,89%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>7,57%</t>
+          <t>7,66%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -8104,12 +8104,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>407652</t>
+          <t>411313</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>495291</t>
+          <t>501099</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -8119,12 +8119,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>7,19%</t>
         </is>
       </c>
     </row>
@@ -8304,7 +8304,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si en el barrio donde vive el ruido procedente del exterior de su vivienda le resulta molesto en 2016</t>
+          <t>Población según si en el barrio donde vive el ruido procedente del exterior de su vivienda le resulta molesto en 2016 (tasa de respuesta: 99,89%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -8499,12 +8499,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>289972</t>
+          <t>291068</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>325333</t>
+          <t>327014</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8514,12 +8514,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>69,13%</t>
+          <t>69,39%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>77,56%</t>
+          <t>77,96%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8534,12 +8534,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>256521</t>
+          <t>254836</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>291822</t>
+          <t>291464</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8549,12 +8549,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>64,82%</t>
+          <t>64,39%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>73,74%</t>
+          <t>73,65%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8569,12 +8569,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>554187</t>
+          <t>555650</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>606154</t>
+          <t>609532</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8584,12 +8584,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>67,98%</t>
+          <t>68,16%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>74,35%</t>
+          <t>74,77%</t>
         </is>
       </c>
     </row>
@@ -8612,12 +8612,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>69598</t>
+          <t>69709</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>102325</t>
+          <t>102682</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8627,12 +8627,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>16,59%</t>
+          <t>16,62%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>24,39%</t>
+          <t>24,48%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8647,12 +8647,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>80787</t>
+          <t>80123</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>115244</t>
+          <t>114723</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8662,12 +8662,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>20,41%</t>
+          <t>20,25%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>29,12%</t>
+          <t>28,99%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8682,12 +8682,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>160296</t>
+          <t>159185</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>206911</t>
+          <t>207139</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8697,12 +8697,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>19,66%</t>
+          <t>19,53%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>25,38%</t>
+          <t>25,41%</t>
         </is>
       </c>
     </row>
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>16378</t>
+          <t>16406</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>36420</t>
+          <t>37232</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8740,12 +8740,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>8,68%</t>
+          <t>8,88%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -8760,12 +8760,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>16511</t>
+          <t>16699</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>36223</t>
+          <t>35665</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8775,12 +8775,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>9,15%</t>
+          <t>9,01%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -8795,12 +8795,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>37321</t>
+          <t>37282</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>66684</t>
+          <t>64957</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8810,12 +8810,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>8,18%</t>
+          <t>7,97%</t>
         </is>
       </c>
     </row>
@@ -8955,12 +8955,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>376661</t>
+          <t>376666</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>421587</t>
+          <t>421123</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8975,7 +8975,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>71,4%</t>
+          <t>71,32%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8990,12 +8990,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>367728</t>
+          <t>368681</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>411352</t>
+          <t>411351</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -9005,7 +9005,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>65,25%</t>
+          <t>65,42%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -9025,12 +9025,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>757310</t>
+          <t>758925</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>819498</t>
+          <t>820219</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -9040,12 +9040,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>65,62%</t>
+          <t>65,76%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>71,01%</t>
+          <t>71,07%</t>
         </is>
       </c>
     </row>
@@ -9068,12 +9068,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>141070</t>
+          <t>142854</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>184858</t>
+          <t>185467</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -9083,12 +9083,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>23,89%</t>
+          <t>24,19%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>31,31%</t>
+          <t>31,41%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -9103,12 +9103,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>115070</t>
+          <t>114605</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>152385</t>
+          <t>152457</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -9118,12 +9118,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>20,42%</t>
+          <t>20,34%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>27,04%</t>
+          <t>27,05%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -9138,12 +9138,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>268414</t>
+          <t>267394</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>326884</t>
+          <t>327169</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -9153,12 +9153,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>23,26%</t>
+          <t>23,17%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>28,33%</t>
+          <t>28,35%</t>
         </is>
       </c>
     </row>
@@ -9181,12 +9181,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>18606</t>
+          <t>18684</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>40869</t>
+          <t>40724</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -9196,12 +9196,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,92%</t>
+          <t>6,9%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -9216,12 +9216,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>29115</t>
+          <t>29564</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>53591</t>
+          <t>53197</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -9231,12 +9231,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>9,51%</t>
+          <t>9,44%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9251,12 +9251,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>52836</t>
+          <t>54346</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>85384</t>
+          <t>86520</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -9266,12 +9266,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>4,71%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,4%</t>
+          <t>7,5%</t>
         </is>
       </c>
     </row>
@@ -9411,12 +9411,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>449387</t>
+          <t>448263</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>498639</t>
+          <t>497965</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -9426,12 +9426,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>67,16%</t>
+          <t>67,0%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>74,52%</t>
+          <t>74,42%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -9446,12 +9446,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>459105</t>
+          <t>460114</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>504050</t>
+          <t>505570</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -9461,12 +9461,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>69,53%</t>
+          <t>69,68%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>76,34%</t>
+          <t>76,57%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -9481,12 +9481,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>927848</t>
+          <t>922722</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>992284</t>
+          <t>989531</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9496,12 +9496,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>69,79%</t>
+          <t>69,41%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>74,64%</t>
+          <t>74,43%</t>
         </is>
       </c>
     </row>
@@ -9524,12 +9524,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>137164</t>
+          <t>138477</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>180413</t>
+          <t>182131</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9539,12 +9539,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>20,5%</t>
+          <t>20,7%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>26,96%</t>
+          <t>27,22%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9559,12 +9559,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>113584</t>
+          <t>111405</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>152348</t>
+          <t>152850</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9574,12 +9574,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>17,2%</t>
+          <t>16,87%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>23,07%</t>
+          <t>23,15%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9594,12 +9594,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>261360</t>
+          <t>262701</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>322725</t>
+          <t>323200</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9609,12 +9609,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>19,66%</t>
+          <t>19,76%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>24,28%</t>
+          <t>24,31%</t>
         </is>
       </c>
     </row>
@@ -9637,12 +9637,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>25205</t>
+          <t>24757</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>49385</t>
+          <t>49602</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9652,12 +9652,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>7,38%</t>
+          <t>7,41%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9672,12 +9672,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>33083</t>
+          <t>32054</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>60084</t>
+          <t>58946</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9687,12 +9687,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>4,85%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>8,93%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9707,12 +9707,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>64167</t>
+          <t>64569</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>98882</t>
+          <t>101500</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9722,12 +9722,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>4,86%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>7,44%</t>
+          <t>7,63%</t>
         </is>
       </c>
     </row>
@@ -9867,12 +9867,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>437150</t>
+          <t>436613</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>482348</t>
+          <t>486345</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -9882,12 +9882,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>67,91%</t>
+          <t>67,83%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>74,93%</t>
+          <t>75,56%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -9902,12 +9902,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>431253</t>
+          <t>428325</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>480841</t>
+          <t>478457</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9917,12 +9917,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>66,63%</t>
+          <t>66,17%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>74,29%</t>
+          <t>73,92%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9937,12 +9937,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>880312</t>
+          <t>881859</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>949795</t>
+          <t>949574</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9952,12 +9952,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>68,19%</t>
+          <t>68,31%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>73,57%</t>
+          <t>73,56%</t>
         </is>
       </c>
     </row>
@@ -9980,12 +9980,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>137654</t>
+          <t>135030</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>180702</t>
+          <t>181793</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9995,12 +9995,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>21,39%</t>
+          <t>20,98%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>28,07%</t>
+          <t>28,24%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10015,12 +10015,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>125436</t>
+          <t>126204</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>171838</t>
+          <t>174324</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -10030,12 +10030,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>19,38%</t>
+          <t>19,5%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>26,55%</t>
+          <t>26,93%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10050,12 +10050,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>275814</t>
+          <t>274819</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>342925</t>
+          <t>336114</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -10065,12 +10065,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>21,36%</t>
+          <t>21,29%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>26,56%</t>
+          <t>26,04%</t>
         </is>
       </c>
     </row>
@@ -10093,12 +10093,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>16089</t>
+          <t>15478</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>37315</t>
+          <t>37087</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -10108,12 +10108,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>5,76%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -10128,12 +10128,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>30897</t>
+          <t>31252</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>56346</t>
+          <t>56864</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -10143,12 +10143,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>8,71%</t>
+          <t>8,79%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -10163,12 +10163,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>52955</t>
+          <t>51921</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>84808</t>
+          <t>87613</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -10178,12 +10178,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>6,79%</t>
         </is>
       </c>
     </row>
@@ -10323,12 +10323,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>324523</t>
+          <t>322439</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>362573</t>
+          <t>364278</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -10338,12 +10338,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>67,9%</t>
+          <t>67,47%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>75,87%</t>
+          <t>76,22%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10358,12 +10358,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>336401</t>
+          <t>335816</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>377568</t>
+          <t>378816</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -10373,12 +10373,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>67,71%</t>
+          <t>67,59%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>75,99%</t>
+          <t>76,24%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10393,12 +10393,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>671462</t>
+          <t>674330</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>732877</t>
+          <t>731260</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -10408,12 +10408,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>68,88%</t>
+          <t>69,18%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>75,18%</t>
+          <t>75,02%</t>
         </is>
       </c>
     </row>
@@ -10436,12 +10436,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>87346</t>
+          <t>83998</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>123110</t>
+          <t>122396</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -10451,12 +10451,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>18,28%</t>
+          <t>17,58%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>25,76%</t>
+          <t>25,61%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -10471,12 +10471,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>87548</t>
+          <t>85648</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>125806</t>
+          <t>123460</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -10486,12 +10486,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>17,62%</t>
+          <t>17,24%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>25,32%</t>
+          <t>24,85%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -10506,12 +10506,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>181261</t>
+          <t>178393</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>235564</t>
+          <t>232742</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -10521,12 +10521,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>18,6%</t>
+          <t>18,3%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>24,17%</t>
+          <t>23,88%</t>
         </is>
       </c>
     </row>
@@ -10549,12 +10549,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>20809</t>
+          <t>20753</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>44567</t>
+          <t>43927</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10564,12 +10564,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,34%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>9,33%</t>
+          <t>9,19%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10584,12 +10584,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>25139</t>
+          <t>24375</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>50068</t>
+          <t>51467</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10599,12 +10599,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>4,91%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>10,08%</t>
+          <t>10,36%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10619,12 +10619,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>50227</t>
+          <t>51127</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>84519</t>
+          <t>83941</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10634,12 +10634,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>8,67%</t>
+          <t>8,61%</t>
         </is>
       </c>
     </row>
@@ -10779,12 +10779,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>221273</t>
+          <t>219941</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>253600</t>
+          <t>254833</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -10794,12 +10794,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>66,18%</t>
+          <t>65,79%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>75,85%</t>
+          <t>76,22%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -10814,12 +10814,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>256638</t>
+          <t>259043</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>293803</t>
+          <t>293965</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -10829,12 +10829,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>68,3%</t>
+          <t>68,94%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>78,19%</t>
+          <t>78,23%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -10849,12 +10849,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>489219</t>
+          <t>489398</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>539541</t>
+          <t>539372</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -10864,12 +10864,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>68,9%</t>
+          <t>68,92%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>75,98%</t>
+          <t>75,96%</t>
         </is>
       </c>
     </row>
@@ -10892,12 +10892,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>64898</t>
+          <t>65299</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>96028</t>
+          <t>98029</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -10907,12 +10907,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>19,41%</t>
+          <t>19,53%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>28,72%</t>
+          <t>29,32%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -10927,12 +10927,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>62419</t>
+          <t>63028</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>94317</t>
+          <t>94871</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -10942,12 +10942,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>16,61%</t>
+          <t>16,77%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>25,1%</t>
+          <t>25,25%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -10962,12 +10962,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>135859</t>
+          <t>135813</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>181165</t>
+          <t>183508</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -10982,7 +10982,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>25,51%</t>
+          <t>25,84%</t>
         </is>
       </c>
     </row>
@@ -11005,12 +11005,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>8855</t>
+          <t>8936</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>24536</t>
+          <t>23353</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -11020,12 +11020,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>7,34%</t>
+          <t>6,98%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -11040,12 +11040,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>13300</t>
+          <t>13438</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>33084</t>
+          <t>32261</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -11055,12 +11055,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>8,8%</t>
+          <t>8,59%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -11075,12 +11075,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>26207</t>
+          <t>25246</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>49145</t>
+          <t>49929</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -11090,12 +11090,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>6,92%</t>
+          <t>7,03%</t>
         </is>
       </c>
     </row>
@@ -11235,12 +11235,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>168156</t>
+          <t>167273</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>193888</t>
+          <t>193670</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -11250,12 +11250,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>65,43%</t>
+          <t>65,09%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>75,44%</t>
+          <t>75,36%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -11270,12 +11270,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>267230</t>
+          <t>267494</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>308910</t>
+          <t>309204</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -11285,12 +11285,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>66,99%</t>
+          <t>67,06%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>77,44%</t>
+          <t>77,51%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -11305,12 +11305,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>442677</t>
+          <t>442463</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>493278</t>
+          <t>492607</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -11320,12 +11320,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>67,49%</t>
+          <t>67,46%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>75,21%</t>
+          <t>75,1%</t>
         </is>
       </c>
     </row>
@@ -11348,12 +11348,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>50286</t>
+          <t>52046</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>75259</t>
+          <t>76508</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -11363,12 +11363,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>19,57%</t>
+          <t>20,25%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>29,28%</t>
+          <t>29,77%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -11383,12 +11383,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>70692</t>
+          <t>69457</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>109304</t>
+          <t>108985</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -11398,12 +11398,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>17,72%</t>
+          <t>17,41%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>27,4%</t>
+          <t>27,32%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -11418,12 +11418,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>128776</t>
+          <t>128188</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>173341</t>
+          <t>174759</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -11433,12 +11433,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>19,63%</t>
+          <t>19,54%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>26,43%</t>
+          <t>26,64%</t>
         </is>
       </c>
     </row>
@@ -11461,12 +11461,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>7633</t>
+          <t>7883</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>20672</t>
+          <t>20804</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -11476,12 +11476,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>8,04%</t>
+          <t>8,09%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -11496,12 +11496,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>13918</t>
+          <t>13175</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>35933</t>
+          <t>35508</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -11511,12 +11511,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>9,01%</t>
+          <t>8,9%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -11531,12 +11531,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>25165</t>
+          <t>24440</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>49261</t>
+          <t>50569</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -11546,12 +11546,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>7,51%</t>
+          <t>7,71%</t>
         </is>
       </c>
     </row>
@@ -11691,12 +11691,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>2358398</t>
+          <t>2352354</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>2463259</t>
+          <t>2465028</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -11706,12 +11706,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>69,53%</t>
+          <t>69,35%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>72,62%</t>
+          <t>72,67%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -11726,12 +11726,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>2471081</t>
+          <t>2468133</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>2579615</t>
+          <t>2574743</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -11741,12 +11741,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>69,84%</t>
+          <t>69,75%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>72,9%</t>
+          <t>72,77%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -11761,12 +11761,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>4857914</t>
+          <t>4855485</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>5011271</t>
+          <t>5017726</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -11776,12 +11776,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>70,1%</t>
+          <t>70,06%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>72,31%</t>
+          <t>72,4%</t>
         </is>
       </c>
     </row>
@@ -11804,12 +11804,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>760183</t>
+          <t>760094</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>856771</t>
+          <t>867740</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -11824,7 +11824,7 @@
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>25,26%</t>
+          <t>25,58%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -11839,12 +11839,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>731642</t>
+          <t>727895</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>830463</t>
+          <t>831038</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -11854,12 +11854,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>20,68%</t>
+          <t>20,57%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>23,47%</t>
+          <t>23,49%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -11874,12 +11874,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>1523261</t>
+          <t>1515835</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>1665136</t>
+          <t>1664846</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -11889,12 +11889,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>21,98%</t>
+          <t>21,87%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>24,03%</t>
+          <t>24,02%</t>
         </is>
       </c>
     </row>
@@ -11917,12 +11917,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>149034</t>
+          <t>146103</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>200082</t>
+          <t>198607</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -11932,12 +11932,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>5,86%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -11952,12 +11952,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>204263</t>
+          <t>204163</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>261565</t>
+          <t>265938</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -11972,7 +11972,7 @@
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>7,39%</t>
+          <t>7,52%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -11987,12 +11987,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>364726</t>
+          <t>365690</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>446020</t>
+          <t>446835</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -12002,12 +12002,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>6,44%</t>
+          <t>6,45%</t>
         </is>
       </c>
     </row>
@@ -12187,7 +12187,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si en el barrio donde vive el ruido procedente del exterior de su vivienda le resulta molesto en 2023</t>
+          <t>Población según si en el barrio donde vive el ruido procedente del exterior de su vivienda le resulta molesto en 2023 (tasa de respuesta: 99,92%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -12382,12 +12382,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>299434</t>
+          <t>302735</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>352196</t>
+          <t>353550</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -12397,12 +12397,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>74,86%</t>
+          <t>75,69%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>88,05%</t>
+          <t>88,39%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -12417,12 +12417,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>190711</t>
+          <t>190525</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>234340</t>
+          <t>238063</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -12432,12 +12432,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>60,89%</t>
+          <t>60,83%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>74,82%</t>
+          <t>76,01%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -12452,12 +12452,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>508915</t>
+          <t>507570</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>577977</t>
+          <t>579481</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -12467,12 +12467,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>71,36%</t>
+          <t>71,17%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>81,04%</t>
+          <t>81,25%</t>
         </is>
       </c>
     </row>
@@ -12495,12 +12495,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>35539</t>
+          <t>34949</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>81650</t>
+          <t>81210</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -12510,12 +12510,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>8,89%</t>
+          <t>8,74%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>20,41%</t>
+          <t>20,3%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -12530,12 +12530,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>52237</t>
+          <t>51822</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>95006</t>
+          <t>92303</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -12545,12 +12545,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>16,68%</t>
+          <t>16,55%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>30,33%</t>
+          <t>29,47%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -12565,12 +12565,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>94798</t>
+          <t>97372</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>158196</t>
+          <t>161939</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -12580,12 +12580,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>13,29%</t>
+          <t>13,65%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>22,18%</t>
+          <t>22,71%</t>
         </is>
       </c>
     </row>
@@ -12608,12 +12608,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>6771</t>
+          <t>6334</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>30753</t>
+          <t>30554</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -12623,12 +12623,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>7,69%</t>
+          <t>7,64%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -12643,12 +12643,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>15943</t>
+          <t>15572</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>44017</t>
+          <t>41199</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -12658,12 +12658,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>4,97%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>14,05%</t>
+          <t>13,15%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -12678,12 +12678,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>27290</t>
+          <t>25587</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>62093</t>
+          <t>62793</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -12693,12 +12693,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>8,71%</t>
+          <t>8,8%</t>
         </is>
       </c>
     </row>
@@ -12838,12 +12838,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>291705</t>
+          <t>289887</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>337182</t>
+          <t>335059</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -12853,12 +12853,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>68,87%</t>
+          <t>68,44%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>79,61%</t>
+          <t>79,11%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -12873,12 +12873,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>400043</t>
+          <t>399532</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>457907</t>
+          <t>458620</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -12888,12 +12888,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>78,12%</t>
+          <t>78,02%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>89,42%</t>
+          <t>89,56%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -12908,12 +12908,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>704830</t>
+          <t>703562</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>784258</t>
+          <t>782844</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -12923,12 +12923,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>75,33%</t>
+          <t>75,2%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>83,82%</t>
+          <t>83,67%</t>
         </is>
       </c>
     </row>
@@ -12951,12 +12951,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>64167</t>
+          <t>64763</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>106401</t>
+          <t>105274</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -12966,12 +12966,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>15,15%</t>
+          <t>15,29%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>25,12%</t>
+          <t>24,86%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -12986,12 +12986,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>38369</t>
+          <t>36886</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>82551</t>
+          <t>83378</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -13001,12 +13001,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>7,49%</t>
+          <t>7,2%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>16,12%</t>
+          <t>16,28%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -13021,12 +13021,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>112346</t>
+          <t>114458</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>175856</t>
+          <t>176355</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -13036,12 +13036,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>12,01%</t>
+          <t>12,23%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>18,8%</t>
+          <t>18,85%</t>
         </is>
       </c>
     </row>
@@ -13064,12 +13064,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>14401</t>
+          <t>14830</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>39897</t>
+          <t>40779</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -13079,12 +13079,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>9,42%</t>
+          <t>9,63%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -13099,12 +13099,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>13627</t>
+          <t>14919</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>37588</t>
+          <t>38354</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -13114,12 +13114,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,34%</t>
+          <t>7,49%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -13134,12 +13134,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>33845</t>
+          <t>32808</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>68062</t>
+          <t>68371</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -13149,12 +13149,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,27%</t>
+          <t>7,31%</t>
         </is>
       </c>
     </row>
@@ -13294,12 +13294,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>395499</t>
+          <t>391237</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>436145</t>
+          <t>433662</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -13309,12 +13309,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>73,93%</t>
+          <t>73,13%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>81,52%</t>
+          <t>81,06%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -13329,12 +13329,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>455238</t>
+          <t>454543</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>505680</t>
+          <t>504493</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -13344,12 +13344,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>77,1%</t>
+          <t>76,99%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>85,65%</t>
+          <t>85,45%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -13364,12 +13364,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>858956</t>
+          <t>858909</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>921902</t>
+          <t>921442</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -13384,7 +13384,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>81,92%</t>
+          <t>81,88%</t>
         </is>
       </c>
     </row>
@@ -13407,12 +13407,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>77540</t>
+          <t>78258</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>114660</t>
+          <t>115545</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -13422,12 +13422,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>14,49%</t>
+          <t>14,63%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>21,43%</t>
+          <t>21,6%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -13442,12 +13442,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>58538</t>
+          <t>60607</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>97917</t>
+          <t>97938</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -13457,12 +13457,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>9,91%</t>
+          <t>10,27%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>16,58%</t>
+          <t>16,59%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -13477,12 +13477,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>148195</t>
+          <t>149102</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>204539</t>
+          <t>203841</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -13492,12 +13492,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>13,17%</t>
+          <t>13,25%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>18,17%</t>
+          <t>18,11%</t>
         </is>
       </c>
     </row>
@@ -13520,12 +13520,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>15860</t>
+          <t>15199</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>35831</t>
+          <t>36436</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -13535,12 +13535,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>6,81%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -13555,12 +13555,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>24643</t>
+          <t>25043</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>45768</t>
+          <t>45308</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -13570,12 +13570,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>7,75%</t>
+          <t>7,67%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -13590,12 +13590,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>45612</t>
+          <t>45041</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>75814</t>
+          <t>73789</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -13605,12 +13605,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>6,74%</t>
+          <t>6,56%</t>
         </is>
       </c>
     </row>
@@ -13750,12 +13750,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>663892</t>
+          <t>666287</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>815498</t>
+          <t>823473</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -13765,12 +13765,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>74,78%</t>
+          <t>75,05%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>91,86%</t>
+          <t>92,76%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -13785,12 +13785,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>523428</t>
+          <t>524720</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>570158</t>
+          <t>574153</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -13800,12 +13800,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>73,42%</t>
+          <t>73,61%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>79,98%</t>
+          <t>80,54%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -13820,12 +13820,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1209397</t>
+          <t>1207412</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1418807</t>
+          <t>1395029</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -13835,12 +13835,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>75,56%</t>
+          <t>75,43%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>88,64%</t>
+          <t>87,15%</t>
         </is>
       </c>
     </row>
@@ -13863,12 +13863,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>49887</t>
+          <t>48551</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>156898</t>
+          <t>158277</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -13878,12 +13878,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>5,47%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>17,67%</t>
+          <t>17,83%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -13898,12 +13898,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>109007</t>
+          <t>107583</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>147170</t>
+          <t>147491</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -13913,12 +13913,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>15,29%</t>
+          <t>15,09%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>20,64%</t>
+          <t>20,69%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -13933,12 +13933,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>140749</t>
+          <t>151695</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>288637</t>
+          <t>290424</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -13948,12 +13948,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>8,79%</t>
+          <t>9,48%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>18,03%</t>
+          <t>18,14%</t>
         </is>
       </c>
     </row>
@@ -13976,12 +13976,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>19508</t>
+          <t>19651</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>80084</t>
+          <t>77327</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -13991,12 +13991,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>9,02%</t>
+          <t>8,71%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -14011,12 +14011,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>29508</t>
+          <t>28405</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>49305</t>
+          <t>49095</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -14026,12 +14026,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>6,92%</t>
+          <t>6,89%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -14046,12 +14046,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>49925</t>
+          <t>53397</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>115822</t>
+          <t>114630</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -14061,12 +14061,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>7,24%</t>
+          <t>7,16%</t>
         </is>
       </c>
     </row>
@@ -14206,12 +14206,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>420140</t>
+          <t>416817</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>455888</t>
+          <t>454608</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -14221,12 +14221,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>74,97%</t>
+          <t>74,38%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>81,35%</t>
+          <t>81,12%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -14241,12 +14241,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>408152</t>
+          <t>407408</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>438154</t>
+          <t>436987</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -14256,12 +14256,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>74,66%</t>
+          <t>74,52%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>80,15%</t>
+          <t>79,94%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -14276,12 +14276,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>837811</t>
+          <t>836820</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>883732</t>
+          <t>883291</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -14291,12 +14291,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>75,68%</t>
+          <t>75,59%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>79,83%</t>
+          <t>79,79%</t>
         </is>
       </c>
     </row>
@@ -14319,12 +14319,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>75390</t>
+          <t>75236</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>107296</t>
+          <t>109836</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -14334,12 +14334,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>13,45%</t>
+          <t>13,43%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>19,15%</t>
+          <t>19,6%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -14354,12 +14354,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>72217</t>
+          <t>72165</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>98185</t>
+          <t>98080</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -14369,12 +14369,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>13,21%</t>
+          <t>13,2%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>17,96%</t>
+          <t>17,94%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -14389,12 +14389,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>155623</t>
+          <t>156681</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>197032</t>
+          <t>200185</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -14404,12 +14404,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>14,06%</t>
+          <t>14,15%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>17,8%</t>
+          <t>18,08%</t>
         </is>
       </c>
     </row>
@@ -14432,12 +14432,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>23319</t>
+          <t>22379</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>43431</t>
+          <t>43255</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -14447,12 +14447,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>7,75%</t>
+          <t>7,72%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -14467,12 +14467,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>30906</t>
+          <t>30864</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>48719</t>
+          <t>48967</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -14487,7 +14487,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>8,91%</t>
+          <t>8,96%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -14502,12 +14502,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>59225</t>
+          <t>58445</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>84496</t>
+          <t>85077</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -14517,12 +14517,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>7,63%</t>
+          <t>7,68%</t>
         </is>
       </c>
     </row>
@@ -14662,12 +14662,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>267090</t>
+          <t>267995</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>292979</t>
+          <t>293891</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -14677,12 +14677,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>72,55%</t>
+          <t>72,79%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>79,58%</t>
+          <t>79,83%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -14697,12 +14697,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>133898</t>
+          <t>147944</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>483826</t>
+          <t>482942</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -14712,12 +14712,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>22,01%</t>
+          <t>24,32%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>79,53%</t>
+          <t>79,38%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -14732,12 +14732,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>322376</t>
+          <t>319832</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>760919</t>
+          <t>759941</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -14747,12 +14747,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>33,01%</t>
+          <t>32,75%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>77,92%</t>
+          <t>77,82%</t>
         </is>
       </c>
     </row>
@@ -14775,12 +14775,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>56699</t>
+          <t>56925</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>80906</t>
+          <t>79773</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -14790,12 +14790,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>15,4%</t>
+          <t>15,46%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>21,98%</t>
+          <t>21,67%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -14810,12 +14810,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>93658</t>
+          <t>93358</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>465755</t>
+          <t>446369</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -14825,12 +14825,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>15,39%</t>
+          <t>15,35%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>76,56%</t>
+          <t>73,37%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -14845,12 +14845,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>162860</t>
+          <t>163381</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>627689</t>
+          <t>633961</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -14860,12 +14860,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>16,68%</t>
+          <t>16,73%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>64,28%</t>
+          <t>64,92%</t>
         </is>
       </c>
     </row>
@@ -14888,12 +14888,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>14325</t>
+          <t>13812</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>28215</t>
+          <t>27981</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -14903,12 +14903,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>7,6%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -14923,12 +14923,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>8078</t>
+          <t>8068</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>34238</t>
+          <t>35035</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -14943,7 +14943,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>5,76%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -14958,12 +14958,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>20749</t>
+          <t>21410</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>56112</t>
+          <t>58063</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -14973,12 +14973,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>5,95%</t>
         </is>
       </c>
     </row>
@@ -15118,12 +15118,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>201367</t>
+          <t>200662</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>223909</t>
+          <t>224414</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -15133,12 +15133,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>71,22%</t>
+          <t>70,97%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>79,19%</t>
+          <t>79,37%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -15153,12 +15153,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>322519</t>
+          <t>323304</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>349000</t>
+          <t>347970</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -15168,12 +15168,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>75,74%</t>
+          <t>75,92%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>81,96%</t>
+          <t>81,72%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -15188,12 +15188,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>532350</t>
+          <t>533164</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>567114</t>
+          <t>565464</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -15203,12 +15203,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>75,13%</t>
+          <t>75,24%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>80,03%</t>
+          <t>79,8%</t>
         </is>
       </c>
     </row>
@@ -15231,12 +15231,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>47702</t>
+          <t>48256</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>70427</t>
+          <t>70844</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -15246,12 +15246,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>16,87%</t>
+          <t>17,07%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>24,91%</t>
+          <t>25,05%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -15266,12 +15266,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>61375</t>
+          <t>61607</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>84954</t>
+          <t>85070</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -15281,12 +15281,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>14,41%</t>
+          <t>14,47%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>19,95%</t>
+          <t>19,98%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -15301,12 +15301,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>116223</t>
+          <t>117413</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>147309</t>
+          <t>147544</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -15316,12 +15316,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>16,4%</t>
+          <t>16,57%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>20,79%</t>
+          <t>20,82%</t>
         </is>
       </c>
     </row>
@@ -15344,12 +15344,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>6293</t>
+          <t>6524</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>16611</t>
+          <t>16213</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -15359,12 +15359,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>5,73%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -15379,12 +15379,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>11377</t>
+          <t>11393</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>24445</t>
+          <t>24201</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -15394,12 +15394,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>5,68%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -15414,12 +15414,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>19304</t>
+          <t>20150</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>36220</t>
+          <t>37133</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -15429,12 +15429,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>5,24%</t>
         </is>
       </c>
     </row>
@@ -15574,12 +15574,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>2648396</t>
+          <t>2644107</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>2893326</t>
+          <t>2895736</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -15589,12 +15589,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>76,6%</t>
+          <t>76,47%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>83,68%</t>
+          <t>83,75%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -15609,12 +15609,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>2225091</t>
+          <t>2236442</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>2915021</t>
+          <t>2910916</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -15624,12 +15624,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>59,98%</t>
+          <t>60,29%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>78,58%</t>
+          <t>78,47%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -15644,12 +15644,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>4915344</t>
+          <t>4847633</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>5682650</t>
+          <t>5661836</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -15659,12 +15659,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>68,58%</t>
+          <t>67,64%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>79,29%</t>
+          <t>79,0%</t>
         </is>
       </c>
     </row>
@@ -15687,12 +15687,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>438998</t>
+          <t>433685</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>621307</t>
+          <t>625530</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -15702,12 +15702,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>12,7%</t>
+          <t>12,54%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>17,97%</t>
+          <t>18,09%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -15722,12 +15722,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>587980</t>
+          <t>587837</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>1326205</t>
+          <t>1312426</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -15742,7 +15742,7 @@
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>35,75%</t>
+          <t>35,38%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -15757,12 +15757,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>1116765</t>
+          <t>1130477</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>1950911</t>
+          <t>2068696</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -15772,12 +15772,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>15,58%</t>
+          <t>15,77%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>27,22%</t>
+          <t>28,86%</t>
         </is>
       </c>
     </row>
@@ -15800,12 +15800,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>131385</t>
+          <t>134441</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>209956</t>
+          <t>211718</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -15815,12 +15815,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>6,12%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -15835,12 +15835,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>165751</t>
+          <t>163137</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>231197</t>
+          <t>230764</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -15850,12 +15850,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>6,23%</t>
+          <t>6,22%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -15870,12 +15870,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>318560</t>
+          <t>314345</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>428628</t>
+          <t>423616</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -15885,12 +15885,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>5,91%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P05A01-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P05A01-Edad-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>251764</t>
+          <t>250754</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>296051</t>
+          <t>294033</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>50,96%</t>
+          <t>50,75%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>59,92%</t>
+          <t>59,51%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>227492</t>
+          <t>226116</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>268973</t>
+          <t>268753</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>48,77%</t>
+          <t>48,47%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>57,66%</t>
+          <t>57,61%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>489892</t>
+          <t>493621</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>551171</t>
+          <t>553745</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>51,0%</t>
+          <t>51,39%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>57,38%</t>
+          <t>57,65%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>162622</t>
+          <t>163450</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>204020</t>
+          <t>205724</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>32,92%</t>
+          <t>33,08%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>41,29%</t>
+          <t>41,64%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>147425</t>
+          <t>149348</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>186821</t>
+          <t>188508</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>31,6%</t>
+          <t>32,01%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>40,05%</t>
+          <t>40,41%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>323199</t>
+          <t>322777</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>380645</t>
+          <t>379748</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>33,65%</t>
+          <t>33,6%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>39,63%</t>
+          <t>39,53%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>27118</t>
+          <t>25731</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>49759</t>
+          <t>48789</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>5,21%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>10,07%</t>
+          <t>9,88%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>39644</t>
+          <t>39256</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>67120</t>
+          <t>65383</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>8,5%</t>
+          <t>8,42%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>14,39%</t>
+          <t>14,02%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>71762</t>
+          <t>70998</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>105504</t>
+          <t>104734</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>7,47%</t>
+          <t>7,39%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>10,98%</t>
+          <t>10,9%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>371077</t>
+          <t>370149</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>425404</t>
+          <t>425885</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>50,45%</t>
+          <t>50,33%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>57,84%</t>
+          <t>57,9%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>267316</t>
+          <t>266158</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>320005</t>
+          <t>319646</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>42,74%</t>
+          <t>42,55%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>51,16%</t>
+          <t>51,1%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>654811</t>
+          <t>656589</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>728398</t>
+          <t>727714</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>48,11%</t>
+          <t>48,24%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>53,52%</t>
+          <t>53,47%</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>236467</t>
+          <t>237177</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>286742</t>
+          <t>290984</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>32,15%</t>
+          <t>32,25%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>38,99%</t>
+          <t>39,56%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>230780</t>
+          <t>233803</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>281346</t>
+          <t>284398</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1352,12 +1352,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>36,9%</t>
+          <t>37,38%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>44,98%</t>
+          <t>45,47%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>480314</t>
+          <t>484714</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>556571</t>
+          <t>554635</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>35,29%</t>
+          <t>35,62%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>40,89%</t>
+          <t>40,75%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>57689</t>
+          <t>57429</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>93022</t>
+          <t>93292</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>7,84%</t>
+          <t>7,81%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>12,65%</t>
+          <t>12,68%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>57902</t>
+          <t>58009</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>92550</t>
+          <t>91566</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>9,26%</t>
+          <t>9,27%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>14,8%</t>
+          <t>14,64%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>125384</t>
+          <t>124689</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>172580</t>
+          <t>171429</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>9,21%</t>
+          <t>9,16%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>12,68%</t>
+          <t>12,6%</t>
         </is>
       </c>
     </row>
@@ -1645,12 +1645,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>315138</t>
+          <t>313457</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>366006</t>
+          <t>366508</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1660,12 +1660,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>49,34%</t>
+          <t>49,08%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>57,31%</t>
+          <t>57,39%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1680,12 +1680,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>313240</t>
+          <t>315386</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>369023</t>
+          <t>367624</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1695,12 +1695,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>45,41%</t>
+          <t>45,73%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>53,5%</t>
+          <t>53,3%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1715,12 +1715,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>643125</t>
+          <t>645599</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>718098</t>
+          <t>718367</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1730,12 +1730,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>48,41%</t>
+          <t>48,6%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>54,06%</t>
+          <t>54,08%</t>
         </is>
       </c>
     </row>
@@ -1758,12 +1758,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>215685</t>
+          <t>214233</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>266172</t>
+          <t>265981</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1773,12 +1773,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>33,77%</t>
+          <t>33,54%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>41,68%</t>
+          <t>41,65%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1793,12 +1793,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>216305</t>
+          <t>214748</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>267118</t>
+          <t>266937</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1808,12 +1808,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>31,36%</t>
+          <t>31,13%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>38,73%</t>
+          <t>38,7%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1828,12 +1828,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>446514</t>
+          <t>445884</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>515699</t>
+          <t>515453</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1843,12 +1843,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>33,61%</t>
+          <t>33,57%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>38,82%</t>
+          <t>38,8%</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>44761</t>
+          <t>43943</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>75639</t>
+          <t>73507</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>7,01%</t>
+          <t>6,88%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>11,84%</t>
+          <t>11,51%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>89000</t>
+          <t>91132</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>129242</t>
+          <t>131254</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>12,9%</t>
+          <t>13,21%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>18,74%</t>
+          <t>19,03%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>143452</t>
+          <t>144495</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>194335</t>
+          <t>194022</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>10,8%</t>
+          <t>10,88%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>14,63%</t>
+          <t>14,61%</t>
         </is>
       </c>
     </row>
@@ -2101,12 +2101,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>247685</t>
+          <t>246648</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>295820</t>
+          <t>295448</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2116,12 +2116,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>47,71%</t>
+          <t>47,51%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>56,98%</t>
+          <t>56,91%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2136,12 +2136,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>246353</t>
+          <t>248324</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>292279</t>
+          <t>293255</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2151,12 +2151,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>47,95%</t>
+          <t>48,34%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>56,89%</t>
+          <t>57,08%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>510492</t>
+          <t>509393</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>574539</t>
+          <t>573386</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2186,12 +2186,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>49,42%</t>
+          <t>49,32%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>55,62%</t>
+          <t>55,51%</t>
         </is>
       </c>
     </row>
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>168924</t>
+          <t>169082</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>214556</t>
+          <t>215458</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2229,12 +2229,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>32,54%</t>
+          <t>32,57%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>41,33%</t>
+          <t>41,5%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2249,12 +2249,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>153570</t>
+          <t>150282</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>195571</t>
+          <t>193778</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2264,12 +2264,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>29,89%</t>
+          <t>29,25%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>38,07%</t>
+          <t>37,72%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2284,12 +2284,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>333256</t>
+          <t>333466</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>396457</t>
+          <t>394031</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>32,26%</t>
+          <t>32,29%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>38,38%</t>
+          <t>38,15%</t>
         </is>
       </c>
     </row>
@@ -2327,12 +2327,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>42818</t>
+          <t>42897</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>70399</t>
+          <t>71089</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2342,12 +2342,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>8,25%</t>
+          <t>8,26%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>13,56%</t>
+          <t>13,69%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2362,12 +2362,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>57147</t>
+          <t>55296</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>87824</t>
+          <t>86907</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2377,12 +2377,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>11,12%</t>
+          <t>10,76%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>17,1%</t>
+          <t>16,92%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2397,12 +2397,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>108146</t>
+          <t>106750</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>150788</t>
+          <t>150709</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2412,12 +2412,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>10,47%</t>
+          <t>10,34%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>14,6%</t>
+          <t>14,59%</t>
         </is>
       </c>
     </row>
@@ -2557,12 +2557,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>179828</t>
+          <t>179880</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>219523</t>
+          <t>218609</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2572,12 +2572,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>46,6%</t>
+          <t>46,62%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>56,89%</t>
+          <t>56,65%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2592,12 +2592,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>186700</t>
+          <t>187778</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>226440</t>
+          <t>227206</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2607,12 +2607,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>46,32%</t>
+          <t>46,59%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>56,18%</t>
+          <t>56,37%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>380167</t>
+          <t>377965</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>432258</t>
+          <t>433140</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2642,12 +2642,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>48,19%</t>
+          <t>47,91%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>54,79%</t>
+          <t>54,9%</t>
         </is>
       </c>
     </row>
@@ -2670,12 +2670,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>120758</t>
+          <t>120501</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>157750</t>
+          <t>157557</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2685,12 +2685,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>31,3%</t>
+          <t>31,23%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>40,88%</t>
+          <t>40,83%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2705,12 +2705,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>114281</t>
+          <t>114879</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>151141</t>
+          <t>151505</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2720,12 +2720,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>28,35%</t>
+          <t>28,5%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>37,5%</t>
+          <t>37,59%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2740,12 +2740,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>244957</t>
+          <t>246493</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>297801</t>
+          <t>297223</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2755,12 +2755,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>31,05%</t>
+          <t>31,24%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>37,75%</t>
+          <t>37,67%</t>
         </is>
       </c>
     </row>
@@ -2783,12 +2783,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>35715</t>
+          <t>36616</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>62384</t>
+          <t>62158</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2798,12 +2798,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>9,26%</t>
+          <t>9,49%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>16,17%</t>
+          <t>16,11%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2818,12 +2818,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>50465</t>
+          <t>49930</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>78940</t>
+          <t>79337</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2833,12 +2833,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>12,52%</t>
+          <t>12,39%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>19,59%</t>
+          <t>19,68%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,12 +2853,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>93969</t>
+          <t>91170</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>132060</t>
+          <t>132003</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2868,12 +2868,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>11,91%</t>
+          <t>11,56%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>16,74%</t>
+          <t>16,73%</t>
         </is>
       </c>
     </row>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>127028</t>
+          <t>127658</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>160796</t>
+          <t>162485</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3028,12 +3028,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>43,42%</t>
+          <t>43,63%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>54,96%</t>
+          <t>55,53%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3048,12 +3048,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>150348</t>
+          <t>150279</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>186711</t>
+          <t>185049</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3063,12 +3063,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>43,84%</t>
+          <t>43,82%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>54,45%</t>
+          <t>53,96%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3083,12 +3083,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>288965</t>
+          <t>287885</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>334554</t>
+          <t>338522</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3098,12 +3098,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>45,47%</t>
+          <t>45,3%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>52,64%</t>
+          <t>53,27%</t>
         </is>
       </c>
     </row>
@@ -3126,12 +3126,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>102450</t>
+          <t>99859</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>135615</t>
+          <t>136527</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3141,12 +3141,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>35,02%</t>
+          <t>34,13%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>46,35%</t>
+          <t>46,66%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3161,12 +3161,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>111385</t>
+          <t>109897</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>146298</t>
+          <t>143639</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3176,12 +3176,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>32,48%</t>
+          <t>32,05%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>42,66%</t>
+          <t>41,89%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3196,12 +3196,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>224323</t>
+          <t>220397</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>269321</t>
+          <t>267933</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3211,12 +3211,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>35,3%</t>
+          <t>34,68%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>42,38%</t>
+          <t>42,16%</t>
         </is>
       </c>
     </row>
@@ -3239,12 +3239,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>22001</t>
+          <t>21778</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>42081</t>
+          <t>40855</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3254,12 +3254,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>7,52%</t>
+          <t>7,44%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>14,38%</t>
+          <t>13,96%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3274,12 +3274,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>36127</t>
+          <t>35796</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>59384</t>
+          <t>61065</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3289,12 +3289,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>10,53%</t>
+          <t>10,44%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>17,32%</t>
+          <t>17,81%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3309,12 +3309,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>63616</t>
+          <t>62573</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>93399</t>
+          <t>93874</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>10,01%</t>
+          <t>9,85%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>14,7%</t>
+          <t>14,77%</t>
         </is>
       </c>
     </row>
@@ -3469,12 +3469,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>91021</t>
+          <t>90725</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>117825</t>
+          <t>118933</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3484,12 +3484,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>43,55%</t>
+          <t>43,41%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>56,37%</t>
+          <t>56,9%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3504,12 +3504,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>149752</t>
+          <t>148643</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>188050</t>
+          <t>187074</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3519,12 +3519,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>44,85%</t>
+          <t>44,52%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>56,32%</t>
+          <t>56,03%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3539,12 +3539,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>251173</t>
+          <t>249070</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>298803</t>
+          <t>297810</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3554,12 +3554,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>46,26%</t>
+          <t>45,88%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>55,04%</t>
+          <t>54,85%</t>
         </is>
       </c>
     </row>
@@ -3582,12 +3582,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>67919</t>
+          <t>67005</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>94184</t>
+          <t>94391</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3597,12 +3597,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>32,49%</t>
+          <t>32,06%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>45,06%</t>
+          <t>45,16%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3617,12 +3617,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>105716</t>
+          <t>106062</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>143273</t>
+          <t>143430</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3632,12 +3632,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>31,66%</t>
+          <t>31,76%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>42,91%</t>
+          <t>42,95%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3652,12 +3652,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>182948</t>
+          <t>179647</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>227723</t>
+          <t>227474</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3667,12 +3667,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>33,7%</t>
+          <t>33,09%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>41,94%</t>
+          <t>41,9%</t>
         </is>
       </c>
     </row>
@@ -3695,12 +3695,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>14977</t>
+          <t>14881</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>33531</t>
+          <t>32675</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3710,12 +3710,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>7,17%</t>
+          <t>7,12%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>16,04%</t>
+          <t>15,63%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3730,12 +3730,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>28919</t>
+          <t>29303</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>54868</t>
+          <t>54700</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3745,12 +3745,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>8,66%</t>
+          <t>8,78%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>16,43%</t>
+          <t>16,38%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3765,12 +3765,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>50706</t>
+          <t>50197</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>79950</t>
+          <t>81977</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3780,12 +3780,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>9,34%</t>
+          <t>9,25%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>14,73%</t>
+          <t>15,1%</t>
         </is>
       </c>
     </row>
@@ -3925,12 +3925,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>1671606</t>
+          <t>1669534</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>1788804</t>
+          <t>1783761</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3940,12 +3940,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>51,04%</t>
+          <t>50,98%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>54,62%</t>
+          <t>54,47%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3960,12 +3960,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>1638876</t>
+          <t>1638891</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>1753476</t>
+          <t>1756622</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3980,7 +3980,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>51,95%</t>
+          <t>52,04%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3995,12 +3995,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>3340558</t>
+          <t>3349443</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>3503987</t>
+          <t>3512657</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -4010,12 +4010,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>50,23%</t>
+          <t>50,37%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>52,69%</t>
+          <t>52,82%</t>
         </is>
       </c>
     </row>
@@ -4038,12 +4038,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>1162947</t>
+          <t>1164147</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>1272086</t>
+          <t>1273017</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4053,12 +4053,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>35,51%</t>
+          <t>35,55%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>38,84%</t>
+          <t>38,87%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -4073,12 +4073,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>1168849</t>
+          <t>1167324</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>1275453</t>
+          <t>1277303</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4088,12 +4088,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>34,63%</t>
+          <t>34,58%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>37,79%</t>
+          <t>37,84%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4108,12 +4108,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>2360398</t>
+          <t>2353486</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>2519056</t>
+          <t>2514724</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4123,12 +4123,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>35,49%</t>
+          <t>35,39%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>37,88%</t>
+          <t>37,81%</t>
         </is>
       </c>
     </row>
@@ -4151,12 +4151,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>293495</t>
+          <t>294368</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>362341</t>
+          <t>363283</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4166,12 +4166,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>8,96%</t>
+          <t>8,99%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>11,06%</t>
+          <t>11,09%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4186,12 +4186,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>420122</t>
+          <t>411152</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>495299</t>
+          <t>493231</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4201,12 +4201,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>12,45%</t>
+          <t>12,18%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>14,67%</t>
+          <t>14,61%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4221,12 +4221,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>734002</t>
+          <t>734417</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>836581</t>
+          <t>837105</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4241,7 +4241,7 @@
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>12,58%</t>
+          <t>12,59%</t>
         </is>
       </c>
     </row>
@@ -4616,12 +4616,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>295772</t>
+          <t>295410</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>333603</t>
+          <t>334212</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4631,12 +4631,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>65,26%</t>
+          <t>65,18%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>73,61%</t>
+          <t>73,75%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4651,12 +4651,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>292417</t>
+          <t>292126</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>329580</t>
+          <t>328485</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4666,12 +4666,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>68,13%</t>
+          <t>68,06%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>76,79%</t>
+          <t>76,53%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4686,12 +4686,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>597995</t>
+          <t>597911</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>650248</t>
+          <t>651462</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4701,12 +4701,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>67,77%</t>
+          <t>67,76%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>73,69%</t>
+          <t>73,83%</t>
         </is>
       </c>
     </row>
@@ -4729,12 +4729,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>99330</t>
+          <t>100824</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>135693</t>
+          <t>136529</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4744,12 +4744,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>21,92%</t>
+          <t>22,25%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>29,94%</t>
+          <t>30,13%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4764,12 +4764,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>83689</t>
+          <t>85357</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>120217</t>
+          <t>121060</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4779,12 +4779,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>19,5%</t>
+          <t>19,89%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>28,01%</t>
+          <t>28,2%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4799,12 +4799,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>196890</t>
+          <t>193898</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>247648</t>
+          <t>246887</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4814,12 +4814,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>22,31%</t>
+          <t>21,97%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>28,06%</t>
+          <t>27,98%</t>
         </is>
       </c>
     </row>
@@ -4842,12 +4842,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>13690</t>
+          <t>12713</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>31785</t>
+          <t>30832</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4857,12 +4857,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>7,01%</t>
+          <t>6,8%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4877,12 +4877,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>9711</t>
+          <t>10002</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>26742</t>
+          <t>27078</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4892,12 +4892,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>6,23%</t>
+          <t>6,31%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4912,12 +4912,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>26493</t>
+          <t>26571</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>51346</t>
+          <t>51432</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4927,12 +4927,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>5,83%</t>
         </is>
       </c>
     </row>
@@ -5072,12 +5072,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>443922</t>
+          <t>443637</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>492609</t>
+          <t>492589</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5087,12 +5087,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>64,75%</t>
+          <t>64,71%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>71,86%</t>
+          <t>71,85%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5107,12 +5107,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>404928</t>
+          <t>400656</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>451021</t>
+          <t>447386</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5122,12 +5122,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>66,35%</t>
+          <t>65,65%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>73,91%</t>
+          <t>73,31%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5142,12 +5142,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>859078</t>
+          <t>861323</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>926848</t>
+          <t>928592</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5157,12 +5157,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>66,3%</t>
+          <t>66,47%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>71,53%</t>
+          <t>71,66%</t>
         </is>
       </c>
     </row>
@@ -5185,12 +5185,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>147861</t>
+          <t>146037</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>193064</t>
+          <t>192962</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -5200,12 +5200,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>21,57%</t>
+          <t>21,3%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>28,16%</t>
+          <t>28,15%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -5220,12 +5220,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>119327</t>
+          <t>121462</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>161673</t>
+          <t>165359</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5235,12 +5235,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>19,55%</t>
+          <t>19,9%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>26,49%</t>
+          <t>27,1%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -5255,12 +5255,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>280236</t>
+          <t>279360</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>344694</t>
+          <t>340349</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -5270,12 +5270,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>21,63%</t>
+          <t>21,56%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>26,6%</t>
+          <t>26,27%</t>
         </is>
       </c>
     </row>
@@ -5298,12 +5298,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>34398</t>
+          <t>34702</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>62312</t>
+          <t>64237</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5313,12 +5313,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>5,06%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>9,09%</t>
+          <t>9,37%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5333,12 +5333,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>31822</t>
+          <t>32171</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>57753</t>
+          <t>57640</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>5,27%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>9,46%</t>
+          <t>9,45%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5368,12 +5368,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>72108</t>
+          <t>74158</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>111124</t>
+          <t>112279</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>5,72%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>8,58%</t>
+          <t>8,66%</t>
         </is>
       </c>
     </row>
@@ -5528,12 +5528,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>445809</t>
+          <t>447467</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>497533</t>
+          <t>497756</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5543,12 +5543,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>65,54%</t>
+          <t>65,78%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>73,14%</t>
+          <t>73,17%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5563,12 +5563,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>494105</t>
+          <t>497219</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>546901</t>
+          <t>544653</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5578,12 +5578,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>69,68%</t>
+          <t>70,12%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>77,12%</t>
+          <t>76,81%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5598,12 +5598,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>963290</t>
+          <t>960193</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1031869</t>
+          <t>1028657</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5613,12 +5613,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>69,33%</t>
+          <t>69,11%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>74,27%</t>
+          <t>74,04%</t>
         </is>
       </c>
     </row>
@@ -5641,12 +5641,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>144136</t>
+          <t>143585</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>190939</t>
+          <t>190266</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5656,12 +5656,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>21,19%</t>
+          <t>21,11%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>28,07%</t>
+          <t>27,97%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5676,12 +5676,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>121624</t>
+          <t>123910</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>167718</t>
+          <t>169532</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>17,15%</t>
+          <t>17,47%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>23,65%</t>
+          <t>23,91%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5711,12 +5711,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>280317</t>
+          <t>281134</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>340276</t>
+          <t>343459</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>20,18%</t>
+          <t>20,23%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>24,49%</t>
+          <t>24,72%</t>
         </is>
       </c>
     </row>
@@ -5754,12 +5754,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>29216</t>
+          <t>29595</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>55638</t>
+          <t>55349</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5769,12 +5769,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>8,18%</t>
+          <t>8,14%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5789,12 +5789,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>31748</t>
+          <t>32972</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>59042</t>
+          <t>59000</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,65%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>8,33%</t>
+          <t>8,32%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5824,12 +5824,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>66570</t>
+          <t>67262</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>103084</t>
+          <t>103892</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>4,84%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>7,48%</t>
         </is>
       </c>
     </row>
@@ -5984,12 +5984,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>387189</t>
+          <t>387082</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>437604</t>
+          <t>437862</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5999,12 +5999,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>63,1%</t>
+          <t>63,08%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>71,32%</t>
+          <t>71,36%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6019,12 +6019,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>407559</t>
+          <t>407049</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>454831</t>
+          <t>455598</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>66,25%</t>
+          <t>66,17%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>73,94%</t>
+          <t>74,06%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6054,12 +6054,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>807790</t>
+          <t>807344</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>876533</t>
+          <t>874673</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>65,74%</t>
+          <t>65,71%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>71,34%</t>
+          <t>71,19%</t>
         </is>
       </c>
     </row>
@@ -6097,12 +6097,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>138321</t>
+          <t>137884</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>186280</t>
+          <t>184848</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6112,12 +6112,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>22,54%</t>
+          <t>22,47%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>30,36%</t>
+          <t>30,13%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6132,12 +6132,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>110898</t>
+          <t>110330</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>153857</t>
+          <t>153177</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>18,03%</t>
+          <t>17,94%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>25,01%</t>
+          <t>24,9%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6167,12 +6167,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>261175</t>
+          <t>266632</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>327232</t>
+          <t>325474</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>21,26%</t>
+          <t>21,7%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>26,63%</t>
+          <t>26,49%</t>
         </is>
       </c>
     </row>
@@ -6210,12 +6210,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>30022</t>
+          <t>28740</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>55718</t>
+          <t>58110</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -6225,12 +6225,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>9,08%</t>
+          <t>9,47%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6245,12 +6245,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>39112</t>
+          <t>38071</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>69337</t>
+          <t>68464</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6260,12 +6260,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>6,19%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>11,27%</t>
+          <t>11,13%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6280,12 +6280,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>75732</t>
+          <t>74051</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>114788</t>
+          <t>114081</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6295,12 +6295,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>6,16%</t>
+          <t>6,03%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>9,34%</t>
+          <t>9,28%</t>
         </is>
       </c>
     </row>
@@ -6440,12 +6440,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>284066</t>
+          <t>284174</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>323463</t>
+          <t>323799</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6455,12 +6455,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>66,15%</t>
+          <t>66,17%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>75,32%</t>
+          <t>75,4%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6475,12 +6475,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>283266</t>
+          <t>280060</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>323513</t>
+          <t>323834</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6490,12 +6490,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>63,55%</t>
+          <t>62,83%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>72,58%</t>
+          <t>72,65%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6510,12 +6510,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>578169</t>
+          <t>581129</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>635158</t>
+          <t>638947</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6525,12 +6525,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>66,06%</t>
+          <t>66,4%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>72,58%</t>
+          <t>73,01%</t>
         </is>
       </c>
     </row>
@@ -6553,12 +6553,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>83847</t>
+          <t>84447</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>120075</t>
+          <t>120889</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -6568,12 +6568,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>19,53%</t>
+          <t>19,66%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>27,96%</t>
+          <t>28,15%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -6588,12 +6588,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>91494</t>
+          <t>91859</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>130839</t>
+          <t>129607</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -6603,12 +6603,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>20,53%</t>
+          <t>20,61%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>29,35%</t>
+          <t>29,08%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -6623,12 +6623,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>186943</t>
+          <t>183711</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>241312</t>
+          <t>237667</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -6638,12 +6638,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>21,36%</t>
+          <t>20,99%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>27,57%</t>
+          <t>27,16%</t>
         </is>
       </c>
     </row>
@@ -6666,12 +6666,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>14945</t>
+          <t>15509</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>33923</t>
+          <t>34438</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6681,12 +6681,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>7,9%</t>
+          <t>8,02%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6701,12 +6701,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>22972</t>
+          <t>22478</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>45497</t>
+          <t>45098</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6716,12 +6716,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>5,04%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>10,21%</t>
+          <t>10,12%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6736,12 +6736,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>43037</t>
+          <t>41387</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>71879</t>
+          <t>71210</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6751,12 +6751,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>4,73%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>8,21%</t>
+          <t>8,14%</t>
         </is>
       </c>
     </row>
@@ -6896,12 +6896,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>177572</t>
+          <t>178727</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>214973</t>
+          <t>215836</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6911,12 +6911,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>57,32%</t>
+          <t>57,69%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>69,39%</t>
+          <t>69,67%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6931,12 +6931,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>217266</t>
+          <t>220358</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>252985</t>
+          <t>255487</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6946,12 +6946,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>61,38%</t>
+          <t>62,25%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>71,47%</t>
+          <t>72,17%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6966,12 +6966,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>407119</t>
+          <t>404518</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>457939</t>
+          <t>456117</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6981,12 +6981,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>61,33%</t>
+          <t>60,94%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>68,99%</t>
+          <t>68,71%</t>
         </is>
       </c>
     </row>
@@ -7009,12 +7009,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>67331</t>
+          <t>67196</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>100418</t>
+          <t>99931</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -7024,12 +7024,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>21,73%</t>
+          <t>21,69%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>32,42%</t>
+          <t>32,26%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -7044,12 +7044,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>73477</t>
+          <t>72695</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>106360</t>
+          <t>106319</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>20,76%</t>
+          <t>20,54%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>30,05%</t>
+          <t>30,03%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -7079,12 +7079,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>149428</t>
+          <t>149921</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>196578</t>
+          <t>195941</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -7094,12 +7094,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>22,51%</t>
+          <t>22,59%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>29,61%</t>
+          <t>29,52%</t>
         </is>
       </c>
     </row>
@@ -7122,12 +7122,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>20462</t>
+          <t>19593</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>42770</t>
+          <t>43072</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -7137,12 +7137,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>6,32%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>13,81%</t>
+          <t>13,9%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -7157,12 +7157,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>19214</t>
+          <t>19376</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>40616</t>
+          <t>41718</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -7172,12 +7172,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>5,47%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>11,47%</t>
+          <t>11,78%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -7192,12 +7192,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>45186</t>
+          <t>43792</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>76645</t>
+          <t>76185</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -7207,12 +7207,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>6,81%</t>
+          <t>6,6%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>11,55%</t>
+          <t>11,48%</t>
         </is>
       </c>
     </row>
@@ -7352,12 +7352,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>153335</t>
+          <t>154856</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>185423</t>
+          <t>185327</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -7367,12 +7367,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>61,66%</t>
+          <t>62,27%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>74,56%</t>
+          <t>74,52%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -7387,12 +7387,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>248171</t>
+          <t>247943</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>286998</t>
+          <t>286664</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -7402,12 +7402,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>63,8%</t>
+          <t>63,74%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>73,78%</t>
+          <t>73,7%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -7422,12 +7422,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>413941</t>
+          <t>408993</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>460226</t>
+          <t>458959</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -7437,12 +7437,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>64,92%</t>
+          <t>64,14%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>72,17%</t>
+          <t>71,98%</t>
         </is>
       </c>
     </row>
@@ -7465,12 +7465,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>50740</t>
+          <t>52259</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>80795</t>
+          <t>81025</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7480,12 +7480,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>20,4%</t>
+          <t>21,01%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>32,49%</t>
+          <t>32,58%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7500,12 +7500,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>84556</t>
+          <t>84980</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>121769</t>
+          <t>122049</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7515,12 +7515,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>21,74%</t>
+          <t>21,85%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>31,3%</t>
+          <t>31,38%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7535,12 +7535,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>145407</t>
+          <t>148452</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>191199</t>
+          <t>194651</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7550,12 +7550,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>22,8%</t>
+          <t>23,28%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>29,98%</t>
+          <t>30,53%</t>
         </is>
       </c>
     </row>
@@ -7578,12 +7578,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>7321</t>
+          <t>7886</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>22424</t>
+          <t>22354</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7593,12 +7593,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>9,02%</t>
+          <t>8,99%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7613,12 +7613,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>11801</t>
+          <t>11567</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>29114</t>
+          <t>30364</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7628,12 +7628,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>7,48%</t>
+          <t>7,81%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7648,12 +7648,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>22871</t>
+          <t>23319</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>46400</t>
+          <t>47596</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7663,12 +7663,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>7,28%</t>
+          <t>7,46%</t>
         </is>
       </c>
     </row>
@@ -7808,12 +7808,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>2286459</t>
+          <t>2290496</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>2394117</t>
+          <t>2393800</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -7823,12 +7823,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>66,85%</t>
+          <t>66,96%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>69,99%</t>
+          <t>69,98%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -7843,12 +7843,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>2435719</t>
+          <t>2436516</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>2551859</t>
+          <t>2545187</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -7858,12 +7858,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>68,56%</t>
+          <t>68,59%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>71,83%</t>
+          <t>71,65%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -7878,12 +7878,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>4765199</t>
+          <t>4763795</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>4919501</t>
+          <t>4919165</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -7893,7 +7893,7 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>68,34%</t>
+          <t>68,32%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
@@ -7921,12 +7921,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>813418</t>
+          <t>812155</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>917529</t>
+          <t>910383</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -7936,12 +7936,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>23,78%</t>
+          <t>23,74%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>26,82%</t>
+          <t>26,62%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -7956,12 +7956,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>767178</t>
+          <t>773694</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>872355</t>
+          <t>878396</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -7971,12 +7971,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>21,6%</t>
+          <t>21,78%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>24,56%</t>
+          <t>24,73%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -7991,12 +7991,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>1614482</t>
+          <t>1604287</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>1749883</t>
+          <t>1753728</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -8006,12 +8006,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>23,15%</t>
+          <t>23,01%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>25,1%</t>
+          <t>25,15%</t>
         </is>
       </c>
     </row>
@@ -8034,12 +8034,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>188398</t>
+          <t>189308</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>248313</t>
+          <t>248372</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -8049,7 +8049,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>5,51%</t>
+          <t>5,53%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -8069,12 +8069,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>209362</t>
+          <t>208493</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>271966</t>
+          <t>268588</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -8084,12 +8084,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>5,87%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>7,56%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -8104,12 +8104,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>411313</t>
+          <t>413728</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>501099</t>
+          <t>499674</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -8119,12 +8119,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>5,93%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>7,19%</t>
+          <t>7,17%</t>
         </is>
       </c>
     </row>
@@ -8499,12 +8499,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>291068</t>
+          <t>290117</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>327014</t>
+          <t>325136</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8514,12 +8514,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>69,39%</t>
+          <t>69,16%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>77,96%</t>
+          <t>77,51%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8534,12 +8534,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>254836</t>
+          <t>255246</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>291464</t>
+          <t>290703</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8549,12 +8549,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>64,39%</t>
+          <t>64,5%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>73,65%</t>
+          <t>73,46%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8569,12 +8569,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>555650</t>
+          <t>557937</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>609532</t>
+          <t>608475</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8584,12 +8584,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>68,16%</t>
+          <t>68,44%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>74,77%</t>
+          <t>74,64%</t>
         </is>
       </c>
     </row>
@@ -8612,12 +8612,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>69709</t>
+          <t>71129</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>102682</t>
+          <t>102703</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8627,7 +8627,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>16,62%</t>
+          <t>16,96%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -8647,12 +8647,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>80123</t>
+          <t>81986</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>114723</t>
+          <t>114644</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8662,12 +8662,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>20,25%</t>
+          <t>20,72%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>28,99%</t>
+          <t>28,97%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8682,12 +8682,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>159185</t>
+          <t>160911</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>207139</t>
+          <t>205798</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8697,12 +8697,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>19,53%</t>
+          <t>19,74%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>25,41%</t>
+          <t>25,24%</t>
         </is>
       </c>
     </row>
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>16406</t>
+          <t>16348</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>37232</t>
+          <t>37285</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8740,12 +8740,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>8,88%</t>
+          <t>8,89%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -8760,12 +8760,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>16699</t>
+          <t>16885</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>35665</t>
+          <t>35045</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8775,12 +8775,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>9,01%</t>
+          <t>8,86%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -8795,12 +8795,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>37282</t>
+          <t>38212</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>64957</t>
+          <t>66101</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8810,12 +8810,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>7,97%</t>
+          <t>8,11%</t>
         </is>
       </c>
     </row>
@@ -8955,12 +8955,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>376666</t>
+          <t>376140</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>421123</t>
+          <t>422233</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8970,12 +8970,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>63,79%</t>
+          <t>63,7%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>71,32%</t>
+          <t>71,5%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8990,12 +8990,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>368681</t>
+          <t>370605</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>411351</t>
+          <t>412365</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -9005,12 +9005,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>65,42%</t>
+          <t>65,76%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>72,99%</t>
+          <t>73,17%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9025,12 +9025,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>758925</t>
+          <t>755862</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>820219</t>
+          <t>820457</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -9040,12 +9040,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>65,76%</t>
+          <t>65,5%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>71,07%</t>
+          <t>71,09%</t>
         </is>
       </c>
     </row>
@@ -9068,12 +9068,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>142854</t>
+          <t>143548</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>185467</t>
+          <t>187655</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -9083,12 +9083,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>24,19%</t>
+          <t>24,31%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>31,41%</t>
+          <t>31,78%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -9103,12 +9103,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>114605</t>
+          <t>111551</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>152457</t>
+          <t>151187</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -9118,12 +9118,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>20,34%</t>
+          <t>19,79%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>27,05%</t>
+          <t>26,83%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -9138,12 +9138,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>267394</t>
+          <t>268289</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>327169</t>
+          <t>325991</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -9153,12 +9153,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>23,17%</t>
+          <t>23,25%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>28,35%</t>
+          <t>28,25%</t>
         </is>
       </c>
     </row>
@@ -9181,12 +9181,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>18684</t>
+          <t>18938</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>40724</t>
+          <t>39970</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -9196,12 +9196,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,9%</t>
+          <t>6,77%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -9216,12 +9216,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>29564</t>
+          <t>29416</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>53197</t>
+          <t>53204</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -9231,7 +9231,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>5,22%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -9251,12 +9251,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>54346</t>
+          <t>52766</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>86520</t>
+          <t>86578</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -9266,7 +9266,7 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -9411,12 +9411,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>448263</t>
+          <t>449338</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>497965</t>
+          <t>497971</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -9426,7 +9426,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>67,0%</t>
+          <t>67,16%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -9446,12 +9446,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>460114</t>
+          <t>458894</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>505570</t>
+          <t>503203</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -9461,12 +9461,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>69,68%</t>
+          <t>69,5%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>76,57%</t>
+          <t>76,21%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -9481,12 +9481,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>922722</t>
+          <t>921880</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>989531</t>
+          <t>987574</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9496,12 +9496,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>69,41%</t>
+          <t>69,35%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>74,43%</t>
+          <t>74,29%</t>
         </is>
       </c>
     </row>
@@ -9524,12 +9524,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>138477</t>
+          <t>136550</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>182131</t>
+          <t>184018</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9539,12 +9539,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>20,7%</t>
+          <t>20,41%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>27,22%</t>
+          <t>27,5%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9559,12 +9559,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>111405</t>
+          <t>114620</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>152850</t>
+          <t>155066</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9574,12 +9574,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>16,87%</t>
+          <t>17,36%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>23,15%</t>
+          <t>23,48%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9594,12 +9594,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>262701</t>
+          <t>263555</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>323200</t>
+          <t>326351</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9609,12 +9609,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>19,76%</t>
+          <t>19,83%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>24,31%</t>
+          <t>24,55%</t>
         </is>
       </c>
     </row>
@@ -9637,12 +9637,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>24757</t>
+          <t>25377</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>49602</t>
+          <t>50027</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9652,12 +9652,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>7,41%</t>
+          <t>7,48%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9672,12 +9672,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>32054</t>
+          <t>33061</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>58946</t>
+          <t>59243</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9687,12 +9687,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>8,93%</t>
+          <t>8,97%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9707,12 +9707,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>64569</t>
+          <t>64953</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>101500</t>
+          <t>100282</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9722,12 +9722,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>4,89%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>7,63%</t>
+          <t>7,54%</t>
         </is>
       </c>
     </row>
@@ -9867,12 +9867,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>436613</t>
+          <t>437442</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>486345</t>
+          <t>486102</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -9882,12 +9882,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>67,83%</t>
+          <t>67,96%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>75,56%</t>
+          <t>75,52%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -9902,12 +9902,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>428325</t>
+          <t>430426</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>478457</t>
+          <t>476950</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9917,12 +9917,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>66,17%</t>
+          <t>66,5%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>73,92%</t>
+          <t>73,69%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9937,12 +9937,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>881859</t>
+          <t>884752</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>949574</t>
+          <t>950333</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9952,12 +9952,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>68,31%</t>
+          <t>68,53%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>73,56%</t>
+          <t>73,61%</t>
         </is>
       </c>
     </row>
@@ -9980,12 +9980,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>135030</t>
+          <t>133820</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>181793</t>
+          <t>180045</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9995,12 +9995,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>20,98%</t>
+          <t>20,79%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>28,24%</t>
+          <t>27,97%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10015,12 +10015,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>126204</t>
+          <t>130112</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>174324</t>
+          <t>172091</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -10030,12 +10030,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>19,5%</t>
+          <t>20,1%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>26,93%</t>
+          <t>26,59%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10050,12 +10050,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>274819</t>
+          <t>274765</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>336114</t>
+          <t>337638</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -10065,12 +10065,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>21,29%</t>
+          <t>21,28%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>26,04%</t>
+          <t>26,15%</t>
         </is>
       </c>
     </row>
@@ -10093,12 +10093,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>15478</t>
+          <t>16694</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>37087</t>
+          <t>38499</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -10108,12 +10108,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>5,98%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -10128,12 +10128,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>31252</t>
+          <t>30043</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>56864</t>
+          <t>56946</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -10143,12 +10143,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>8,79%</t>
+          <t>8,8%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -10163,12 +10163,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>51921</t>
+          <t>52453</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>87613</t>
+          <t>84049</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -10178,12 +10178,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>6,79%</t>
+          <t>6,51%</t>
         </is>
       </c>
     </row>
@@ -10323,12 +10323,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>322439</t>
+          <t>322233</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>364278</t>
+          <t>363532</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -10338,12 +10338,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>67,47%</t>
+          <t>67,42%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>76,22%</t>
+          <t>76,07%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10358,12 +10358,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>335816</t>
+          <t>333503</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>378816</t>
+          <t>376118</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -10373,12 +10373,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>67,59%</t>
+          <t>67,12%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>76,24%</t>
+          <t>75,7%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10393,12 +10393,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>674330</t>
+          <t>671712</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>731260</t>
+          <t>730546</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -10408,12 +10408,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>69,18%</t>
+          <t>68,91%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>75,02%</t>
+          <t>74,95%</t>
         </is>
       </c>
     </row>
@@ -10436,12 +10436,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>83998</t>
+          <t>84503</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>122396</t>
+          <t>122922</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -10451,12 +10451,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>17,58%</t>
+          <t>17,68%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>25,61%</t>
+          <t>25,72%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -10471,12 +10471,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>85648</t>
+          <t>86461</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>123460</t>
+          <t>122547</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -10486,12 +10486,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>17,24%</t>
+          <t>17,4%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>24,85%</t>
+          <t>24,66%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -10506,12 +10506,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>178393</t>
+          <t>180654</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>232742</t>
+          <t>233282</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -10521,12 +10521,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>18,3%</t>
+          <t>18,53%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>23,88%</t>
+          <t>23,93%</t>
         </is>
       </c>
     </row>
@@ -10549,12 +10549,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>20753</t>
+          <t>21382</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>43927</t>
+          <t>43800</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10564,12 +10564,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>9,19%</t>
+          <t>9,16%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10584,12 +10584,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>24375</t>
+          <t>24093</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>51467</t>
+          <t>50080</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10599,12 +10599,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>4,85%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>10,36%</t>
+          <t>10,08%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10619,12 +10619,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>51127</t>
+          <t>49970</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>83941</t>
+          <t>83839</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10634,12 +10634,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>5,13%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>8,61%</t>
+          <t>8,6%</t>
         </is>
       </c>
     </row>
@@ -10779,12 +10779,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>219941</t>
+          <t>222960</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>254833</t>
+          <t>255869</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -10794,12 +10794,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>65,79%</t>
+          <t>66,69%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>76,22%</t>
+          <t>76,53%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -10814,12 +10814,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>259043</t>
+          <t>259196</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>293965</t>
+          <t>293803</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -10829,12 +10829,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>68,94%</t>
+          <t>68,98%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>78,23%</t>
+          <t>78,19%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -10849,12 +10849,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>489398</t>
+          <t>490568</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>539372</t>
+          <t>539449</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -10864,12 +10864,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>68,92%</t>
+          <t>69,09%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>75,96%</t>
+          <t>75,97%</t>
         </is>
       </c>
     </row>
@@ -10892,12 +10892,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>65299</t>
+          <t>63332</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>98029</t>
+          <t>94942</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -10907,12 +10907,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>19,53%</t>
+          <t>18,94%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>29,32%</t>
+          <t>28,4%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -10927,12 +10927,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>63028</t>
+          <t>63087</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>94871</t>
+          <t>95501</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -10942,12 +10942,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>16,77%</t>
+          <t>16,79%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>25,25%</t>
+          <t>25,42%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -10962,12 +10962,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>135813</t>
+          <t>137264</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>183508</t>
+          <t>181933</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -10977,12 +10977,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>19,13%</t>
+          <t>19,33%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>25,84%</t>
+          <t>25,62%</t>
         </is>
       </c>
     </row>
@@ -11005,12 +11005,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>8936</t>
+          <t>8865</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>23353</t>
+          <t>22919</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -11020,12 +11020,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>6,98%</t>
+          <t>6,86%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -11040,12 +11040,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>13438</t>
+          <t>13362</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>32261</t>
+          <t>31758</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -11055,12 +11055,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>8,59%</t>
+          <t>8,45%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -11075,12 +11075,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>25246</t>
+          <t>25484</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>49929</t>
+          <t>49450</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -11090,12 +11090,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>7,03%</t>
+          <t>6,96%</t>
         </is>
       </c>
     </row>
@@ -11235,12 +11235,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>167273</t>
+          <t>166407</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>193670</t>
+          <t>193047</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -11250,12 +11250,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>65,09%</t>
+          <t>64,75%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>75,36%</t>
+          <t>75,12%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -11270,12 +11270,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>267494</t>
+          <t>266692</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>309204</t>
+          <t>307408</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -11285,12 +11285,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>67,06%</t>
+          <t>66,86%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>77,51%</t>
+          <t>77,06%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -11305,12 +11305,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>442463</t>
+          <t>444844</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>492607</t>
+          <t>494164</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -11320,12 +11320,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>67,46%</t>
+          <t>67,82%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>75,1%</t>
+          <t>75,34%</t>
         </is>
       </c>
     </row>
@@ -11348,12 +11348,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>52046</t>
+          <t>52049</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>76508</t>
+          <t>76113</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -11368,7 +11368,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>29,77%</t>
+          <t>29,62%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -11383,12 +11383,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>69457</t>
+          <t>70945</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>108985</t>
+          <t>107049</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -11398,12 +11398,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>17,41%</t>
+          <t>17,79%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>27,32%</t>
+          <t>26,84%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -11418,12 +11418,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>128188</t>
+          <t>129555</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>174759</t>
+          <t>173616</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -11433,12 +11433,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>19,54%</t>
+          <t>19,75%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>26,64%</t>
+          <t>26,47%</t>
         </is>
       </c>
     </row>
@@ -11461,12 +11461,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>7883</t>
+          <t>7447</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>20804</t>
+          <t>20538</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -11476,12 +11476,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>8,09%</t>
+          <t>7,99%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -11496,12 +11496,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>13175</t>
+          <t>12727</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>35508</t>
+          <t>35010</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -11511,12 +11511,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>8,9%</t>
+          <t>8,78%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -11531,12 +11531,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>24440</t>
+          <t>24350</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>50569</t>
+          <t>50532</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -11546,12 +11546,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>7,71%</t>
+          <t>7,7%</t>
         </is>
       </c>
     </row>
@@ -11691,12 +11691,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>2352354</t>
+          <t>2356632</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>2465028</t>
+          <t>2459967</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -11706,12 +11706,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>69,35%</t>
+          <t>69,48%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>72,67%</t>
+          <t>72,52%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -11726,12 +11726,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>2468133</t>
+          <t>2469825</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>2574743</t>
+          <t>2579641</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -11741,12 +11741,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>69,75%</t>
+          <t>69,8%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>72,77%</t>
+          <t>72,9%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -11761,12 +11761,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>4855485</t>
+          <t>4859903</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>5017726</t>
+          <t>5007627</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -11776,12 +11776,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>70,06%</t>
+          <t>70,12%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>72,4%</t>
+          <t>72,26%</t>
         </is>
       </c>
     </row>
@@ -11804,12 +11804,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>760094</t>
+          <t>761850</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>867740</t>
+          <t>864703</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -11819,12 +11819,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>22,41%</t>
+          <t>22,46%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>25,58%</t>
+          <t>25,49%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -11839,12 +11839,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>727895</t>
+          <t>730528</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>831038</t>
+          <t>833360</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -11854,12 +11854,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>20,57%</t>
+          <t>20,65%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>23,49%</t>
+          <t>23,55%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -11874,12 +11874,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>1515835</t>
+          <t>1524787</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>1664846</t>
+          <t>1660712</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -11889,12 +11889,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>21,87%</t>
+          <t>22,0%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>24,02%</t>
+          <t>23,96%</t>
         </is>
       </c>
     </row>
@@ -11917,12 +11917,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>146103</t>
+          <t>150494</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>198607</t>
+          <t>202754</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -11932,12 +11932,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,44%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>5,98%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -11952,12 +11952,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>204163</t>
+          <t>203539</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>265938</t>
+          <t>261542</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -11967,12 +11967,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>5,75%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>7,52%</t>
+          <t>7,39%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -11987,12 +11987,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>365690</t>
+          <t>368422</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>446835</t>
+          <t>444543</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -12002,12 +12002,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>5,32%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>6,45%</t>
+          <t>6,41%</t>
         </is>
       </c>
     </row>
@@ -12377,32 +12377,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>330654</t>
+          <t>336332</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>302735</t>
+          <t>314083</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>353550</t>
+          <t>360111</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>82,67%</t>
+          <t>82,48%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>75,69%</t>
+          <t>77,02%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>88,39%</t>
+          <t>88,31%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -12412,32 +12412,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>214755</t>
+          <t>248551</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>190525</t>
+          <t>225038</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>238063</t>
+          <t>274129</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>68,57%</t>
+          <t>68,56%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>60,83%</t>
+          <t>62,08%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>76,01%</t>
+          <t>75,62%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -12447,32 +12447,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>545409</t>
+          <t>584884</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>507570</t>
+          <t>551005</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>579481</t>
+          <t>620235</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>76,47%</t>
+          <t>75,93%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>71,17%</t>
+          <t>71,53%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>81,25%</t>
+          <t>80,52%</t>
         </is>
       </c>
     </row>
@@ -12490,22 +12490,22 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>54590</t>
+          <t>56062</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>34949</t>
+          <t>35659</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>81210</t>
+          <t>79118</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>13,65%</t>
+          <t>13,75%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -12515,7 +12515,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>20,3%</t>
+          <t>19,4%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -12525,32 +12525,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>71696</t>
+          <t>80263</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>51822</t>
+          <t>59495</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>92303</t>
+          <t>102956</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>22,89%</t>
+          <t>22,14%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>16,55%</t>
+          <t>16,41%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>29,47%</t>
+          <t>28,4%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -12560,32 +12560,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>126286</t>
+          <t>136325</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>97372</t>
+          <t>107698</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>161939</t>
+          <t>168041</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>17,71%</t>
+          <t>17,7%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>13,65%</t>
+          <t>13,98%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>22,71%</t>
+          <t>21,81%</t>
         </is>
       </c>
     </row>
@@ -12603,32 +12603,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>14743</t>
+          <t>15399</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>6334</t>
+          <t>7256</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>30554</t>
+          <t>28849</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>7,64%</t>
+          <t>7,07%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -12638,32 +12638,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>26749</t>
+          <t>33698</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>15572</t>
+          <t>22218</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>41199</t>
+          <t>51214</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>8,54%</t>
+          <t>9,3%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>6,13%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>13,15%</t>
+          <t>14,13%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -12673,32 +12673,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>41492</t>
+          <t>49097</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>25587</t>
+          <t>32312</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>62793</t>
+          <t>69532</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>6,37%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>8,8%</t>
+          <t>9,03%</t>
         </is>
       </c>
     </row>
@@ -12716,17 +12716,17 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -12751,17 +12751,17 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -12786,17 +12786,17 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -12833,32 +12833,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>314375</t>
+          <t>347551</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>289887</t>
+          <t>321948</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>335059</t>
+          <t>373131</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>74,22%</t>
+          <t>72,88%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>68,44%</t>
+          <t>67,51%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>79,11%</t>
+          <t>78,24%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -12868,32 +12868,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>423976</t>
+          <t>402786</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>399532</t>
+          <t>384121</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>458620</t>
+          <t>419900</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>82,79%</t>
+          <t>80,28%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>78,02%</t>
+          <t>76,56%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>89,56%</t>
+          <t>83,69%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -12903,32 +12903,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>738351</t>
+          <t>750337</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>703562</t>
+          <t>713648</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>782844</t>
+          <t>777065</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>78,91%</t>
+          <t>76,67%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>75,2%</t>
+          <t>72,92%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>83,67%</t>
+          <t>79,4%</t>
         </is>
       </c>
     </row>
@@ -12946,32 +12946,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>84510</t>
+          <t>102488</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>64763</t>
+          <t>80894</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>105274</t>
+          <t>126944</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>19,95%</t>
+          <t>21,49%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>15,29%</t>
+          <t>16,96%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>24,86%</t>
+          <t>26,62%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -12981,32 +12981,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>63064</t>
+          <t>72662</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>36886</t>
+          <t>58373</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>83378</t>
+          <t>90582</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>12,31%</t>
+          <t>14,48%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>11,63%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>16,28%</t>
+          <t>18,05%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -13016,32 +13016,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>147574</t>
+          <t>175149</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>114458</t>
+          <t>149413</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>176355</t>
+          <t>206605</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>15,77%</t>
+          <t>17,9%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>12,23%</t>
+          <t>15,27%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>18,85%</t>
+          <t>21,11%</t>
         </is>
       </c>
     </row>
@@ -13059,32 +13059,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>24662</t>
+          <t>26852</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>14830</t>
+          <t>15255</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>40779</t>
+          <t>41436</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>5,63%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>9,63%</t>
+          <t>8,69%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -13094,32 +13094,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>25053</t>
+          <t>26286</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>14919</t>
+          <t>16930</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>38354</t>
+          <t>37476</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>5,24%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,49%</t>
+          <t>7,47%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -13129,32 +13129,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>49715</t>
+          <t>53137</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>32808</t>
+          <t>39593</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>68371</t>
+          <t>73240</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>5,43%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,31%</t>
+          <t>7,48%</t>
         </is>
       </c>
     </row>
@@ -13172,17 +13172,17 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -13207,17 +13207,17 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>512093</t>
+          <t>501733</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>512093</t>
+          <t>501733</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>512093</t>
+          <t>501733</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -13242,17 +13242,17 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>935640</t>
+          <t>978623</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>935640</t>
+          <t>978623</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>935640</t>
+          <t>978623</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -13289,67 +13289,67 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>415243</t>
+          <t>478765</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>391237</t>
+          <t>455932</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>433662</t>
+          <t>498009</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
+          <t>77,54%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>73,84%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>80,66%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>668</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>482406</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>465093</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>500728</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
           <t>77,62%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>73,13%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>81,06%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>668</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>473223</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>454543</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>504493</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>80,15%</t>
-        </is>
-      </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>76,99%</t>
+          <t>74,83%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>85,45%</t>
+          <t>80,56%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -13359,32 +13359,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>888466</t>
+          <t>961172</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>858909</t>
+          <t>930913</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>921442</t>
+          <t>989346</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>78,95%</t>
+          <t>77,58%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>76,32%</t>
+          <t>75,14%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>81,88%</t>
+          <t>79,85%</t>
         </is>
       </c>
     </row>
@@ -13402,102 +13402,102 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>95288</t>
+          <t>109299</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>78258</t>
+          <t>90216</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>115545</t>
+          <t>131309</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>17,81%</t>
+          <t>17,7%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
+          <t>14,61%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>21,27%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>126</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>97913</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>81093</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>112955</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>15,75%</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>13,05%</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>18,17%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>215</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>207212</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>181261</t>
+        </is>
+      </c>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>234986</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>16,72%</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
           <t>14,63%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>21,6%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>126</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>82154</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>60607</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>97938</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>13,91%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>10,27%</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>16,59%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>215</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>177442</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>149102</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>203841</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>15,77%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>13,25%</t>
-        </is>
-      </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>18,11%</t>
+          <t>18,97%</t>
         </is>
       </c>
     </row>
@@ -13515,102 +13515,102 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>24458</t>
+          <t>29391</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>15199</t>
+          <t>18731</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>36436</t>
+          <t>42566</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
+          <t>4,76%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>3,03%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>6,89%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>41206</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>32146</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>53542</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>6,63%</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>5,17%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>8,61%</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>70597</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t>56588</t>
+        </is>
+      </c>
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>87979</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>5,7%</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
           <t>4,57%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>2,84%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>6,81%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>52</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>35038</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>25043</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>45308</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>5,93%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>4,24%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>7,67%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>76</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>59497</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>45041</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>73789</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>5,29%</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>4,0%</t>
-        </is>
-      </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>7,1%</t>
         </is>
       </c>
     </row>
@@ -13628,17 +13628,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>534990</t>
+          <t>617455</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>534990</t>
+          <t>617455</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>534990</t>
+          <t>617455</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -13663,17 +13663,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>590415</t>
+          <t>621525</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>590415</t>
+          <t>621525</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>590415</t>
+          <t>621525</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -13698,17 +13698,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1125405</t>
+          <t>1238981</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1125405</t>
+          <t>1238981</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1125405</t>
+          <t>1238981</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -13745,32 +13745,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>734716</t>
+          <t>531449</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>666287</t>
+          <t>506047</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>823473</t>
+          <t>551574</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>82,76%</t>
+          <t>75,85%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>75,05%</t>
+          <t>72,23%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>92,76%</t>
+          <t>78,73%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -13780,32 +13780,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>544709</t>
+          <t>550874</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>524720</t>
+          <t>533237</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>574153</t>
+          <t>569101</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>76,41%</t>
+          <t>74,76%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>73,61%</t>
+          <t>72,36%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>80,54%</t>
+          <t>77,23%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -13815,32 +13815,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>1279425</t>
+          <t>1082324</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1207412</t>
+          <t>1050918</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1395029</t>
+          <t>1111324</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>79,93%</t>
+          <t>75,29%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>75,43%</t>
+          <t>73,11%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>87,15%</t>
+          <t>77,31%</t>
         </is>
       </c>
     </row>
@@ -13858,32 +13858,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>107347</t>
+          <t>126023</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>48551</t>
+          <t>108841</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>158277</t>
+          <t>146664</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>12,09%</t>
+          <t>17,99%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>15,53%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>17,83%</t>
+          <t>20,93%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -13893,32 +13893,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>129647</t>
+          <t>141787</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>107583</t>
+          <t>125492</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>147491</t>
+          <t>158887</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>18,19%</t>
+          <t>19,24%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>15,09%</t>
+          <t>17,03%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>20,69%</t>
+          <t>21,56%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -13928,32 +13928,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>236994</t>
+          <t>267811</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>151695</t>
+          <t>242171</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>290424</t>
+          <t>293579</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>14,81%</t>
+          <t>18,63%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>9,48%</t>
+          <t>16,85%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>18,14%</t>
+          <t>20,42%</t>
         </is>
       </c>
     </row>
@@ -13971,32 +13971,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>45723</t>
+          <t>43144</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>19651</t>
+          <t>31598</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>77327</t>
+          <t>57370</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>6,16%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>4,51%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>8,71%</t>
+          <t>8,19%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -14006,32 +14006,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>38525</t>
+          <t>44224</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>28405</t>
+          <t>35255</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>49095</t>
+          <t>55779</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>6,0%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>6,89%</t>
+          <t>7,57%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -14041,32 +14041,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>84248</t>
+          <t>87369</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>53397</t>
+          <t>72337</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>114630</t>
+          <t>104487</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>6,08%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>5,03%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>7,16%</t>
+          <t>7,27%</t>
         </is>
       </c>
     </row>
@@ -14084,17 +14084,17 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>887786</t>
+          <t>700617</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>887786</t>
+          <t>700617</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>887786</t>
+          <t>700617</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -14119,17 +14119,17 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>712881</t>
+          <t>736886</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>712881</t>
+          <t>736886</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>712881</t>
+          <t>736886</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -14154,17 +14154,17 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>1600667</t>
+          <t>1437504</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1600667</t>
+          <t>1437504</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>1600667</t>
+          <t>1437504</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -14201,32 +14201,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>437694</t>
+          <t>478101</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>416817</t>
+          <t>458110</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>454608</t>
+          <t>497000</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>78,1%</t>
+          <t>78,57%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>74,38%</t>
+          <t>75,29%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>81,12%</t>
+          <t>81,68%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -14236,32 +14236,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>422919</t>
+          <t>469307</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>407408</t>
+          <t>452562</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>436987</t>
+          <t>486243</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>77,36%</t>
+          <t>77,25%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>74,52%</t>
+          <t>74,5%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>79,94%</t>
+          <t>80,04%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -14271,32 +14271,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>860613</t>
+          <t>947408</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>836820</t>
+          <t>920911</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>883291</t>
+          <t>972586</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>77,74%</t>
+          <t>77,91%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>75,59%</t>
+          <t>75,73%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>79,79%</t>
+          <t>79,98%</t>
         </is>
       </c>
     </row>
@@ -14314,32 +14314,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>91079</t>
+          <t>97219</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>75236</t>
+          <t>79962</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>109836</t>
+          <t>115063</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>16,25%</t>
+          <t>15,98%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>13,43%</t>
+          <t>13,14%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>19,6%</t>
+          <t>18,91%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -14349,32 +14349,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>84809</t>
+          <t>94064</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>72165</t>
+          <t>79370</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>98080</t>
+          <t>107964</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>15,51%</t>
+          <t>15,48%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>13,2%</t>
+          <t>13,07%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>17,94%</t>
+          <t>17,77%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -14384,32 +14384,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>175888</t>
+          <t>191283</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>156681</t>
+          <t>166694</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>200185</t>
+          <t>214560</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>15,89%</t>
+          <t>15,73%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>14,15%</t>
+          <t>13,71%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>18,08%</t>
+          <t>17,64%</t>
         </is>
       </c>
     </row>
@@ -14427,32 +14427,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>31627</t>
+          <t>33180</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>22379</t>
+          <t>23987</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>43255</t>
+          <t>44917</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>5,45%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>7,72%</t>
+          <t>7,38%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -14462,27 +14462,27 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>38945</t>
+          <t>44125</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>30864</t>
+          <t>34710</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>48967</t>
+          <t>54411</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>7,12%</t>
+          <t>7,26%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>5,71%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -14497,32 +14497,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>70571</t>
+          <t>77305</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>58445</t>
+          <t>63915</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>85077</t>
+          <t>93584</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>6,37%</t>
+          <t>6,36%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>5,26%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>7,68%</t>
+          <t>7,7%</t>
         </is>
       </c>
     </row>
@@ -14540,17 +14540,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>560399</t>
+          <t>608501</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>560399</t>
+          <t>608501</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>560399</t>
+          <t>608501</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -14575,17 +14575,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>546673</t>
+          <t>607495</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>546673</t>
+          <t>607495</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>546673</t>
+          <t>607495</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -14610,17 +14610,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>1107072</t>
+          <t>1215996</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1107072</t>
+          <t>1215996</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1107072</t>
+          <t>1215996</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -14657,32 +14657,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>280248</t>
+          <t>308581</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>267995</t>
+          <t>293740</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>293891</t>
+          <t>322422</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>76,12%</t>
+          <t>75,8%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>72,79%</t>
+          <t>72,16%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>79,83%</t>
+          <t>79,2%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -14692,32 +14692,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>315583</t>
+          <t>342479</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>147944</t>
+          <t>328486</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>482942</t>
+          <t>355205</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>51,87%</t>
+          <t>77,98%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>24,32%</t>
+          <t>74,8%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>79,38%</t>
+          <t>80,88%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -14727,32 +14727,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>595831</t>
+          <t>651060</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>319832</t>
+          <t>630311</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>759941</t>
+          <t>669720</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>61,01%</t>
+          <t>76,94%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>32,75%</t>
+          <t>74,48%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>77,82%</t>
+          <t>79,14%</t>
         </is>
       </c>
     </row>
@@ -14770,32 +14770,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>67736</t>
+          <t>76024</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>56925</t>
+          <t>63977</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>79773</t>
+          <t>89581</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>18,4%</t>
+          <t>18,68%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>15,46%</t>
+          <t>15,72%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>21,67%</t>
+          <t>22,01%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -14805,32 +14805,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>272189</t>
+          <t>74008</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>93358</t>
+          <t>61906</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>446369</t>
+          <t>85499</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>44,74%</t>
+          <t>16,85%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>15,35%</t>
+          <t>14,1%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>73,37%</t>
+          <t>19,47%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -14840,32 +14840,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>339925</t>
+          <t>150032</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>163381</t>
+          <t>133174</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>633961</t>
+          <t>168670</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>34,81%</t>
+          <t>17,73%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>16,73%</t>
+          <t>15,74%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>64,92%</t>
+          <t>19,93%</t>
         </is>
       </c>
     </row>
@@ -14883,32 +14883,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>20181</t>
+          <t>22475</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>13812</t>
+          <t>15476</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>27981</t>
+          <t>30089</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>5,52%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>7,6%</t>
+          <t>7,39%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -14918,32 +14918,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>20596</t>
+          <t>22679</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>8068</t>
+          <t>16651</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>35035</t>
+          <t>30140</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>5,16%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>6,86%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -14953,32 +14953,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>40777</t>
+          <t>45154</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>21410</t>
+          <t>36273</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>58063</t>
+          <t>55672</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>5,34%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>4,29%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>6,58%</t>
         </is>
       </c>
     </row>
@@ -14996,17 +14996,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>368165</t>
+          <t>407080</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>368165</t>
+          <t>407080</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>368165</t>
+          <t>407080</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -15031,17 +15031,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>608368</t>
+          <t>439166</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>608368</t>
+          <t>439166</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>608368</t>
+          <t>439166</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -15066,17 +15066,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>976533</t>
+          <t>846246</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>976533</t>
+          <t>846246</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>976533</t>
+          <t>846246</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -15113,32 +15113,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>213330</t>
+          <t>231038</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>200662</t>
+          <t>216612</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>224414</t>
+          <t>242362</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>75,45%</t>
+          <t>74,48%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>70,97%</t>
+          <t>69,83%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>79,37%</t>
+          <t>78,13%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -15148,32 +15148,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>336242</t>
+          <t>363480</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>323304</t>
+          <t>349136</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>347970</t>
+          <t>376645</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>78,96%</t>
+          <t>78,23%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>75,92%</t>
+          <t>75,15%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>81,72%</t>
+          <t>81,07%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -15183,32 +15183,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>549573</t>
+          <t>594518</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>533164</t>
+          <t>574393</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>565464</t>
+          <t>612690</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>77,56%</t>
+          <t>76,73%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>75,24%</t>
+          <t>74,13%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>79,8%</t>
+          <t>79,08%</t>
         </is>
       </c>
     </row>
@@ -15226,32 +15226,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>58836</t>
+          <t>67454</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>48256</t>
+          <t>56583</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>70844</t>
+          <t>80706</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>20,81%</t>
+          <t>21,75%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>17,07%</t>
+          <t>18,24%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>25,05%</t>
+          <t>26,02%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -15261,32 +15261,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>73120</t>
+          <t>81984</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>61607</t>
+          <t>70437</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>85070</t>
+          <t>96295</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>17,17%</t>
+          <t>17,65%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>14,47%</t>
+          <t>15,16%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>19,98%</t>
+          <t>20,73%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -15296,32 +15296,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>131956</t>
+          <t>149438</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>117413</t>
+          <t>131949</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>147544</t>
+          <t>168321</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>18,62%</t>
+          <t>19,29%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>16,57%</t>
+          <t>17,03%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>20,82%</t>
+          <t>21,72%</t>
         </is>
       </c>
     </row>
@@ -15339,32 +15339,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>10593</t>
+          <t>11706</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>6524</t>
+          <t>6940</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>16213</t>
+          <t>18623</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,77%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>6,0%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -15374,32 +15374,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>16469</t>
+          <t>19145</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>11393</t>
+          <t>13328</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>24201</t>
+          <t>28634</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>4,12%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>6,16%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -15409,32 +15409,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>27062</t>
+          <t>30851</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>20150</t>
+          <t>22395</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>37133</t>
+          <t>40975</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>5,29%</t>
         </is>
       </c>
     </row>
@@ -15452,17 +15452,17 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -15487,17 +15487,17 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>425831</t>
+          <t>464609</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>425831</t>
+          <t>464609</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>425831</t>
+          <t>464609</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -15522,17 +15522,17 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>708590</t>
+          <t>774807</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>708590</t>
+          <t>774807</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>708590</t>
+          <t>774807</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -15569,32 +15569,32 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>2726260</t>
+          <t>2711819</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>2644107</t>
+          <t>2656245</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>2895736</t>
+          <t>2766267</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>78,85%</t>
+          <t>76,85%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>76,47%</t>
+          <t>75,28%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>83,75%</t>
+          <t>78,4%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -15604,32 +15604,32 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>2731407</t>
+          <t>2859885</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>2236442</t>
+          <t>2816900</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>2910916</t>
+          <t>2908734</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>73,63%</t>
+          <t>76,59%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>60,29%</t>
+          <t>75,44%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>78,47%</t>
+          <t>77,9%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -15639,32 +15639,32 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>5457668</t>
+          <t>5571703</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>4847633</t>
+          <t>5495648</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>5661836</t>
+          <t>5640992</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>76,15%</t>
+          <t>76,72%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>67,64%</t>
+          <t>75,67%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>79,0%</t>
+          <t>77,67%</t>
         </is>
       </c>
     </row>
@@ -15682,32 +15682,32 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>559387</t>
+          <t>634569</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>433685</t>
+          <t>582326</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>625530</t>
+          <t>685706</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>16,18%</t>
+          <t>17,98%</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>12,54%</t>
+          <t>16,5%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>18,09%</t>
+          <t>19,43%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -15717,32 +15717,32 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>776678</t>
+          <t>642681</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>587837</t>
+          <t>600008</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>1312426</t>
+          <t>684501</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>20,94%</t>
+          <t>17,21%</t>
         </is>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>15,85%</t>
+          <t>16,07%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>35,38%</t>
+          <t>18,33%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -15752,32 +15752,32 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>1336065</t>
+          <t>1277250</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>1130477</t>
+          <t>1212134</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>2068696</t>
+          <t>1349294</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
         <is>
-          <t>18,64%</t>
+          <t>17,59%</t>
         </is>
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>15,77%</t>
+          <t>16,69%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>28,86%</t>
+          <t>18,58%</t>
         </is>
       </c>
     </row>
@@ -15795,32 +15795,32 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>171987</t>
+          <t>182148</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>134441</t>
+          <t>154177</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>211718</t>
+          <t>209802</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>5,16%</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>5,95%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -15830,67 +15830,67 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>201375</t>
+          <t>231362</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>163137</t>
+          <t>204668</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>230764</t>
+          <t>258950</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>6,2%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>5,48%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
+          <t>6,94%</t>
+        </is>
+      </c>
+      <c r="Q34" s="2" t="inlineStr">
+        <is>
+          <t>476</t>
+        </is>
+      </c>
+      <c r="R34" s="2" t="inlineStr">
+        <is>
+          <t>413509</t>
+        </is>
+      </c>
+      <c r="S34" s="2" t="inlineStr">
+        <is>
+          <t>372918</t>
+        </is>
+      </c>
+      <c r="T34" s="2" t="inlineStr">
+        <is>
+          <t>451952</t>
+        </is>
+      </c>
+      <c r="U34" s="2" t="inlineStr">
+        <is>
+          <t>5,69%</t>
+        </is>
+      </c>
+      <c r="V34" s="2" t="inlineStr">
+        <is>
+          <t>5,13%</t>
+        </is>
+      </c>
+      <c r="W34" s="2" t="inlineStr">
+        <is>
           <t>6,22%</t>
-        </is>
-      </c>
-      <c r="Q34" s="2" t="inlineStr">
-        <is>
-          <t>476</t>
-        </is>
-      </c>
-      <c r="R34" s="2" t="inlineStr">
-        <is>
-          <t>373362</t>
-        </is>
-      </c>
-      <c r="S34" s="2" t="inlineStr">
-        <is>
-          <t>314345</t>
-        </is>
-      </c>
-      <c r="T34" s="2" t="inlineStr">
-        <is>
-          <t>423616</t>
-        </is>
-      </c>
-      <c r="U34" s="2" t="inlineStr">
-        <is>
-          <t>5,21%</t>
-        </is>
-      </c>
-      <c r="V34" s="2" t="inlineStr">
-        <is>
-          <t>4,39%</t>
-        </is>
-      </c>
-      <c r="W34" s="2" t="inlineStr">
-        <is>
-          <t>5,91%</t>
         </is>
       </c>
     </row>
@@ -15908,17 +15908,17 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>3457634</t>
+          <t>3528535</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>3457634</t>
+          <t>3528535</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>3457634</t>
+          <t>3528535</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -15943,17 +15943,17 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>3709460</t>
+          <t>3733927</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>3709460</t>
+          <t>3733927</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>3709460</t>
+          <t>3733927</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -15978,17 +15978,17 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>7167095</t>
+          <t>7262462</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>7167095</t>
+          <t>7262462</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>7167095</t>
+          <t>7262462</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
